--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORT</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>ÉCHEC</v>
+        <v>Points de code</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>contrôles</v>
+        <v>Courbe de gain</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>S’abonner</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Fermer</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>Adresse e-mail</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>vous@exemple.com</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(facultatif)</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Annuler</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Erreur :</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>Convertir en XML</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>Convertir en JSON</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>Convertir en ICC</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>Conversion en XML…</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>ID du profil</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nom de balise</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Décalage</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Taille</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Rembourrage</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Type</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Tableau de {type}</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>octets</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>Le profil est valide</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>État de validation inconnu</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Valide</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Avertissement</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Erreur</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Inconnu</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Réussi</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Échec</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Détail de validation</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Déclenché par</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Champ</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Valeur actuelle</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Requis : 0</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Attendu : {value}</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>Non valide</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Fermer</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>indentation</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>trier les clés</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Primaires de couleur</v>
+        <v>Environnement</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Détection…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Détection de l’environnement impossible.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Plage complète</v>
+        <v>Gamut étendu</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Plage réduite</v>
+        <v>Chemin canvas HDR</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>sRVB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>oui</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>RAPPORT</v>
+        <v>non</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>ÉCHEC</v>
+        <v>non communiqué</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>contrôles</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Inspecter</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Afficher</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>Outil de profil ICC</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Lire le profil ICC intégré — aucun codec requis</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>S’abonner</v>
+        <v>Afficher les pixels</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Rendu plus lumineux que le blanc</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Décodé par profiletool, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Fermer</v>
+        <v>Les navigateurs ne peuvent pas indiquer la réserve HDR d’un écran, seulement si un chemin HDR existe.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>Adresse e-mail</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>vous@exemple.com</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(facultatif)</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Annuler</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>S’abonner</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Fermer</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Erreur :</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>Convertir en XML</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>Convertir en JSON</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>Convertir en ICC</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>Conversion en XML…</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>Conversion en ICC…</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>Charger un profil ICC</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>ID du profil</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Nom de balise</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Décalage</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Taille</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Rembourrage</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Type</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Tableau de {type}</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>octets</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>Le profil est valide</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Erreur de validation critique</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>État de validation inconnu</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Valide</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Avertissement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Erreur</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Inconnu</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Réussi</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Échec</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Voir dans le contexte</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Détail de validation</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Déclenché par</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Champ</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Valeur actuelle</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Requis : 0</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Attendu : {value}</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>Non valide</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Fermer</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>indentation</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>trier les clés</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>Détection…</v>
+        <v>Affichage du repli SDR</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>Détection de l’environnement impossible.</v>
+        <v>Profil HDR dans la chaîne</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>Écran HDR</v>
+        <v>Les transformations via un profil HDR utilisent son AToB0Tag — le rendu SDR figé exigé par la clause 8.10.6 — car la clause 8.10.1 ne lui laisse aucune balise TRC. Le résultat est ce repli, pas un comportement HDR.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Gamut étendu</v>
+        <v>Ce sont des profils HDR, sans balises TRC : le gamut est donc construit à partir de l’AToB0Tag, le rendu SDR figé qu’exige la clause 8.10.6 pour les consommateurs sans traitement HDR. Ce n’est pas le gamut HDR du profil, qui ne peut être tracé dans un PCS borné.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>Chemin canvas HDR</v>
+        <v>Détection…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRVB</v>
+        <v>Détection de l’environnement impossible.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>aucun</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>oui</v>
+        <v>Gamut étendu</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>non</v>
+        <v>Chemin canvas HDR</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>non communiqué</v>
+        <v>sRVB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Format</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Inspecter</v>
+        <v>oui</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Afficher</v>
+        <v>non</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>non communiqué</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Lire le profil ICC intégré — aucun codec requis</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Afficher les pixels</v>
+        <v>Inspecter</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Rendu plus lumineux que le blanc</v>
+        <v>Afficher</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Décodé par profiletool, donc indépendant du navigateur</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>Les navigateurs ne peuvent pas indiquer la réserve HDR d’un écran, seulement si un chemin HDR existe.</v>
+        <v>Lire le profil ICC intégré — aucun codec requis</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Primaires de couleur</v>
+        <v>Afficher les pixels</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Rendu plus lumineux que le blanc</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Décodé par profiletool, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Les navigateurs ne peuvent pas indiquer la réserve HDR d’un écran, seulement si un chemin HDR existe.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Plage complète</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Plage réduite</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>RAPPORT</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>ÉCHEC</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>contrôles</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>Outil de profil ICC</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>S’abonner</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Fermer</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>Adresse e-mail</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>vous@exemple.com</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(facultatif)</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Annuler</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>S’abonner</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Fermer</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Avis de confidentialité</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Erreur :</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>Convertir en XML</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>Convertir en JSON</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>Convertir en ICC</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>Conversion en XML…</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>ID du profil</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Nom de balise</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Décalage</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Taille</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Rembourrage</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Type</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Tableau de {type}</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>octets</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>Le profil est valide</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>État de validation inconnu</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Avertissement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Erreur</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Inconnu</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Réussi</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Échec</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Détail de validation</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Déclenché par</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Champ</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Valeur actuelle</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Requis : 0</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Attendu : {value}</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>Non valide</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Fermer</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>indentation</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>trier les clés</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Primaires de couleur</v>
+        <v>Options du navigateur</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>activée</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Coefficients de matrice</v>
+        <v>non activée</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>impossible à détecter ici</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Plage complète</v>
+        <v>Nécessaire au rendu HDR dans ce navigateur : sans WebGPU, le canvas HDR est la seule voie. L’inspection des profils fonctionne sans.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Plage réduite</v>
+        <v>Facultatif : le HDR peut passer par WebGPU, mais ceci ajoute la voie canvas HDR et permet à profiletool de lire la vraie réserve HDR de l’écran.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Les pages web ne peuvent pas ouvrir les pages d’options. Collez ceci dans la barre d’adresse, choisissez Enabled, puis relancez le navigateur.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Copier</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Copié</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>RAPPORT</v>
+        <v>Échec de la copie — sélectionnez l’adresse et copiez-la.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>ÉCHEC</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>contrôles</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>S’abonner</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Fermer</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>Adresse e-mail</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>vous@exemple.com</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(facultatif)</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Annuler</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>S’abonner</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Fermer</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Avis de confidentialité</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Erreur :</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>Convertir en XML</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>Convertir en JSON</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>Convertir en ICC</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>Conversion en XML…</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>ID du profil</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Nom de balise</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Décalage</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Taille</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Rembourrage</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Type</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Tableau de {type}</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Aucun contenu)</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>octets</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>Le profil est valide</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Erreur de validation critique</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>État de validation inconnu</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Valide</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Avertissement</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Erreur</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Inconnu</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Réussi</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Échec</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Détail de validation</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Déclenché par</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Champ</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Valeur actuelle</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Requis : 0</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Attendu : {value}</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>Non valide</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Fermer</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>indentation</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>trier les clés</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Les navigateurs ne peuvent pas indiquer la réserve HDR d’un écran, seulement si un chemin HDR existe.</v>
+        <v>Ce navigateur n’a pas indiqué la réserve HDR de l’écran, seulement si un chemin HDR existe.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Primaires de couleur</v>
+        <v>Rapport de pixels</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Écran actuel</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Coefficients de matrice</v>
+        <v>sans nom</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Plage complète</v>
+        <v>intégré</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Plage réduite</v>
+        <v>Réserve HDR</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>non exposée par ce navigateur</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Affichée telle que le navigateur la rapporte. L’unité n’est pas encore normalisée ; un écran SDR a été observé à 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>RAPPORT</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>ÉCHEC</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>contrôles</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>S’abonner</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Fermer</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>Adresse e-mail</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>vous@exemple.com</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(facultatif)</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Annuler</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>S’abonner</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Fermer</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Erreur :</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>Convertir en XML</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>Convertir en JSON</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>Convertir en ICC</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>Conversion en XML…</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>Conversion en JSON…</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>Charger un profil ICC</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>ID du profil</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Nom de balise</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Décalage</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Taille</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Rembourrage</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Type</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Tableau de {type}</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>octets</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>Le profil est valide</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Erreur de validation critique</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>État de validation inconnu</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Valide</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Avertissement</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Erreur</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Inconnu</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Réussi</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Échec</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Détail de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Déclenché par</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Champ</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Valeur actuelle</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Requis : 0</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Attendu : {value}</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>Non valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Fermer</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>indentation</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>trier les clés</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Affichée telle que le navigateur la rapporte. L’unité n’est pas encore normalisée ; un écran SDR a été observé à 0.</v>
+        <v>Chromium l’exprime en diaphragmes : log₂ de la luminance maximale de l’écran ÷ son niveau de blanc SDR. Sous Windows, la valeur n’est actualisée que lorsque Chrome relit l’écran — fenêtre déplacée vers un autre écran ou Chrome réactivé — et non lors d’un changement de luminosité.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>{stops} diaphragmes (≈{ratio}× le blanc SDR)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Identifier les écrans</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Événements d’affichage</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Plage complète</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Plage réduite</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>RAPPORT</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Identifier les écrans</v>
+        <v>Gain pour une réserve d’affichage</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Affichez une image HDR sur cet écran. Les fichiers que le navigateur sait décoder sont affichés par le navigateur lui-même ; OpenEXR est décodé et rendu par profiletool.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Déposez une image HDR ici, ou cliquez pour en choisir une</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>OpenEXR, AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC sous Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>En choisir une autre</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Événements d’affichage</v>
+        <v>Profil ICC intégré</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>aucun — OpenEXR indique la couleur par ses chromaticités</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Primaires de couleur</v>
+        <v>vérification…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Ouvrir dans l’onglet Profil</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Gain map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Plage complète</v>
+        <v>détectée, non décodée</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Plage réduite</v>
+        <v>Ce n’est pas une image. Chargez les profils depuis le panneau Profils.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Format d’image non reconnu par profiletool.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Les pixels TIFF ne sont pas encore affichés ici : les navigateurs ne décodent pas le TIFF, et l’encodage HDR dans un TIFF 16 bits n’est pas encore décidé (phase 4.3). Son profil intégré peut être inspecté.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Impossible d’afficher cette image ici :</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>RAPPORT</v>
+        <v>Son profil intégré peut toutefois être inspecté.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>ÉCHEC</v>
+        <v>Affiché par</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>contrôles</v>
+        <v>le navigateur</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Les navigateurs ignorent le HDR signalé uniquement par un profil ICC intégré ; cette image peut donc paraître terne et plate.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Ce navigateur ne peut pas basculer une image entre SDR et HDR ; elle est affichée telle que le navigateur la rend.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>S’abonner</v>
+        <v>Le navigateur n’a pas pu décoder cette image.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Canevas HDR (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Fermer</v>
+        <v>WebGPU (plage étendue)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Canevas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>Adresse e-mail</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>vous@exemple.com</v>
+        <v>Pixel le plus lumineux</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>{n}× le blanc SDR</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(facultatif)</v>
+        <v>Chromaticités</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>non indiquées — Rec. 709 supposé</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>{from} n’est pas disponible ici ({why}) ; la sortie suivante est utilisée.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Annuler</v>
+        <v>Cette sortie ne peut pas transporter de valeurs plus claires que le blanc ; le rendu SDR après tone mapping est affiché.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>S’abonner</v>
+        <v>Exposition</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>{n} diaphragmes</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Décodage impossible :</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Fermer</v>
+        <v>Décodage…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Plage dynamique</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Erreur :</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>Convertir en XML</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>Convertir en JSON</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>Convertir en ICC</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>Conversion en XML…</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>ID du profil</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Nom de balise</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Décalage</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Taille</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Rembourrage</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Type</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Tableau de {type}</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>octets</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>État de validation inconnu</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Valide</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Avertissement</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Erreur</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Inconnu</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Réussi</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Échec</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Détail de validation</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Déclenché par</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Champ</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Valeur actuelle</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Requis : 0</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Attendu : {value}</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>Non valide</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Fermer</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>indentation</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>trier les clés</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Avis de confidentialité</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Veuillez saisir une adresse e-mail valide.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Erreur réseau. Veuillez réessayer.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Erreur :</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>Convertir en XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>Convertir en JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>Convertir en ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>Conversion en XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>Conversion en JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>Conversion en ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>Charger un profil ICC</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>ID du profil</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>Aucune balise trouvée.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Nom de balise</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Décalage</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Taille</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Rembourrage</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Octets modifiés depuis le chargement</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Type</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Tableau de {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Aucun contenu)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>octets</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>Chargement de la description complète…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>Impossible de charger la description complète :</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Aucune sortie de validation</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>Le profil est valide</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>Le profil comporte des avertissements</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>Le profil est non conforme</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Erreur de validation critique</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>État de validation inconnu</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Critique — affiché à titre d’inspection uniquement</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>Aucun avertissement ni erreur trouvés.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Valide</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Avertissement</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Erreur</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3894,7 +3894,7 @@
         <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain map</v>
+        <v>Carte de gain</v>
       </c>
     </row>
     <row r="437">
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Réserve de l’écran</v>
+        <v>ce navigateur le décode</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>ce navigateur ne le décode pas</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Référence</v>
+        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>reporté à une version ultérieure</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>format inconnu</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>{browser} sous {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>{name} · écran HDR détecté</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>{name} · écran SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Sans changement</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Identifier les écrans</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Événements d’affichage</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Primaires de couleur</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Plage complète</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Plage réduite</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>RAPPORT</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>ÉCHEC</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>contrôles</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>S’abonner</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Fermer</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>Adresse e-mail</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>vous@exemple.com</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(facultatif)</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Annuler</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>S’abonner</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Fermer</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Erreur :</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>Convertir en XML</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>Convertir en JSON</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>Convertir en ICC</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>Conversion en XML…</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>Conversion en JSON…</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>Charger un profil ICC</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>ID du profil</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Nom de balise</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Décalage</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Taille</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Rembourrage</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Type</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Tableau de {type}</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>octets</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>Le profil est valide</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Erreur de validation critique</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>État de validation inconnu</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Valide</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Avertissement</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Erreur</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Inconnu</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Réussi</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Échec</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Détail de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Déclenché par</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Champ</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Valeur actuelle</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Requis : 0</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Attendu : {value}</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>Non valide</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Fermer</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>indentation</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>trier les clés</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Pic de l’écran</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Réserve de l’écran</v>
+        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>1× — écran SDR</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Référence</v>
+        <v>inconnu</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Adapter à l’écran</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>sans limite</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>limite {n} diaphragmes ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Blanc SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Sans changement</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Identifier les écrans</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Événements d’affichage</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Primaires de couleur</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Plage complète</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Plage réduite</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>RAPPORT</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>ÉCHEC</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>contrôles</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>S’abonner</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Fermer</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>Adresse e-mail</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>vous@exemple.com</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(facultatif)</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Annuler</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Erreur :</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>Convertir en XML</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>Convertir en JSON</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>Convertir en ICC</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>Conversion en XML…</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>ID du profil</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Nom de balise</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Décalage</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Taille</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Rembourrage</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Type</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Tableau de {type}</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>octets</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>Le profil est valide</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>État de validation inconnu</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Valide</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Avertissement</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Erreur</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Inconnu</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Réussi</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Échec</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Détail de validation</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Déclenché par</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Champ</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Valeur actuelle</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Requis : 0</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Attendu : {value}</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>Non valide</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Fermer</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>indentation</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>trier les clés</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Pastille blanc SDR</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Référence</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Sans changement</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Identifier les écrans</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Événements d’affichage</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Primaires de couleur</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Plage complète</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Plage réduite</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>RAPPORT</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>ÉCHEC</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>contrôles</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>S’abonner</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>Adresse e-mail</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>vous@exemple.com</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(facultatif)</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Annuler</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>S’abonner</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Fermer</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Erreur :</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>Convertir en JSON</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>ID du profil</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Nom de balise</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Décalage</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Taille</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Rembourrage</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Type</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Tableau de {type}</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>octets</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>Le profil est valide</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>État de validation inconnu</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Valide</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Avertissement</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Erreur</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Inconnu</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Réussi</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Échec</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Détail de validation</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Déclenché par</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Champ</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Valeur actuelle</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Requis : 0</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Attendu : {value}</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>Non valide</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Fermer</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>trier les clés</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Assigner un profil</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Aucun — selon ce qu’indique le fichier</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Profil intégré ({n} o)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Référence</v>
+        <v>Profils HDR du pool</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>profil intégré</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Chemin du moteur couleur</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Chemin HDR, courbe de gain appliquée</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Chemin HDR, sans courbe de gain</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>AToB0 précalculé — pas le chemin HDR</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Transfert</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Blanc de référence HDR</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Sans changement</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>OpenEXR contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Identifier les écrans</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Événements d’affichage</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Plage complète</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Plage réduite</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>RAPPORT</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>ÉCHEC</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>contrôles</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>Outil de profil ICC</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>S’abonner</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Fermer</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>Adresse e-mail</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>vous@exemple.com</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(facultatif)</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Annuler</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>S’abonner</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Fermer</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Avis de confidentialité</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Erreur :</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>Convertir en XML</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>Convertir en JSON</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>Convertir en ICC</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>Conversion en XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>Charger un profil ICC</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>ID du profil</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Nom de balise</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Décalage</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Taille</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Rembourrage</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Type</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Tableau de {type}</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>octets</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>Le profil est valide</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>État de validation inconnu</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Valide</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Avertissement</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Erreur</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Inconnu</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Réussi</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Échec</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Détail de validation</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Déclenché par</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Champ</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Valeur actuelle</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Requis : 0</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Attendu : {value}</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>Non valide</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Fermer</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>indentation</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>trier les clés</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Référence</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>OpenEXR contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Sans changement</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Identifier les écrans</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Événements d’affichage</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Primaires de couleur</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Plage complète</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Plage réduite</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>RAPPORT</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>ÉCHEC</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>contrôles</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>Outil de profil ICC</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>S’abonner</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Fermer</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>Adresse e-mail</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>vous@exemple.com</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(facultatif)</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Annuler</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>S’abonner</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Fermer</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Avis de confidentialité</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Erreur :</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Convertir en XML</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>Convertir en JSON</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>Convertir en ICC</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>Conversion en XML…</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>ID du profil</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Nom de balise</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Décalage</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Taille</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Rembourrage</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Type</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Tableau de {type}</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>octets</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>Le profil est valide</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>Le profil est non conforme</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>État de validation inconnu</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Avertissement</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Erreur</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Inconnu</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Réussi</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Échec</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Détail de validation</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Déclenché par</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Champ</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Valeur actuelle</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Requis : 0</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Attendu : {value}</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>Non valide</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Fermer</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>indentation</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>trier les clés</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Affichez une image HDR sur cet écran. Les fichiers que le navigateur sait décoder sont affichés par le navigateur lui-même ; OpenEXR est décodé et rendu par profiletool.</v>
+        <v>Affichez une image HDR sur cet écran. Les fichiers que le navigateur sait décoder sont affichés par le navigateur lui-même ; OpenEXR et Radiance HDR sont décodés et rendus par profiletool.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC sous Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC sous Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>vérification…</v>
+        <v>aucun — Radiance HDR indique la couleur par son en-tête PRIMARIES</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>aucun</v>
+        <v>vérification…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Ouvrir dans l’onglet Profil</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Carte de gain</v>
+        <v>Ouvrir dans l’onglet Profil</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>détectée, non décodée</v>
+        <v>Carte de gain</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Ce n’est pas une image. Chargez les profils depuis le panneau Profils.</v>
+        <v>détectée, non décodée</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>Format d’image non reconnu par profiletool.</v>
+        <v>Ce n’est pas une image. Chargez les profils depuis le panneau Profils.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>Les pixels TIFF ne sont pas encore affichés ici : les navigateurs ne décodent pas le TIFF, et l’encodage HDR dans un TIFF 16 bits n’est pas encore décidé (phase 4.3). Son profil intégré peut être inspecté.</v>
+        <v>Format d’image non reconnu par profiletool.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossible d’afficher cette image ici :</v>
+        <v>Les pixels TIFF ne sont pas encore affichés ici : les navigateurs ne décodent pas le TIFF, et l’encodage HDR dans un TIFF 16 bits n’est pas encore décidé (phase 4.3). Son profil intégré peut être inspecté.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>Son profil intégré peut toutefois être inspecté.</v>
+        <v>Impossible d’afficher cette image ici :</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Affiché par</v>
+        <v>Son profil intégré peut toutefois être inspecté.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>le navigateur</v>
+        <v>Affiché par</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>le navigateur</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>Écran HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>Les navigateurs ignorent le HDR signalé uniquement par un profil ICC intégré ; cette image peut donc paraître terne et plate.</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Ce navigateur ne peut pas basculer une image entre SDR et HDR ; elle est affichée telle que le navigateur la rend.</v>
+        <v>Les navigateurs ignorent le HDR signalé uniquement par un profil ICC intégré ; cette image peut donc paraître terne et plate.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>Le navigateur n’a pas pu décoder cette image.</v>
+        <v>Ce navigateur ne peut pas basculer une image entre SDR et HDR ; elle est affichée telle que le navigateur la rend.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Sortie</v>
+        <v>Le navigateur n’a pas pu décoder cette image.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>Canevas HDR (float16)</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (plage étendue)</v>
+        <v>Canevas HDR (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>Canevas SDR (tone mapping)</v>
+        <v>WebGPU (plage étendue)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Taille</v>
+        <v>Canevas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Pixel le plus lumineux</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× le blanc SDR</v>
+        <v>Pixel le plus lumineux</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Chromaticités</v>
+        <v>{n}× le blanc SDR</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>non indiquées — Rec. 709 supposé</v>
+        <v>Chromaticités</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} n’est pas disponible ici ({why}) ; la sortie suivante est utilisée.</v>
+        <v>non indiquées — Rec. 709 supposé</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Cette sortie ne peut pas transporter de valeurs plus claires que le blanc ; le rendu SDR après tone mapping est affiché.</v>
+        <v>{from} n’est pas disponible ici ({why}) ; la sortie suivante est utilisée.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Exposition</v>
+        <v>Cette sortie ne peut pas transporter de valeurs plus claires que le blanc ; le rendu SDR après tone mapping est affiché.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} diaphragmes</v>
+        <v>Exposition</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>Décodage impossible :</v>
+        <v>{n} diaphragmes</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>Décodage…</v>
+        <v>Décodage impossible :</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Plage dynamique</v>
+        <v>Décodage…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
+        <v>Plage dynamique</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
+        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>ce navigateur le décode</v>
+        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>ce navigateur ne le décode pas</v>
+        <v>ce navigateur le décode</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
+        <v>ce navigateur ne le décode pas</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
+        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>reporté à une version ultérieure</v>
+        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
+        <v>reporté à une version ultérieure</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
+        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
+        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
+        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
+        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>format inconnu</v>
+        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} sous {os}</v>
+        <v>format inconnu</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · écran HDR détecté</v>
+        <v>{browser} sous {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · écran SDR</v>
+        <v>{name} · écran HDR détecté</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
+        <v>{name} · écran SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
+        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Pic de l’écran</v>
+        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
+        <v>Pic de l’écran</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — écran SDR</v>
+        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>inconnu</v>
+        <v>1× — écran SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
+        <v>inconnu</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
+        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
+        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>Adapter à l’écran</v>
+        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
+        <v>Adapter à l’écran</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>sans limite</v>
+        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>limite {n} diaphragmes ({r}×)</v>
+        <v>sans limite</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>Blanc SDR</v>
+        <v>limite {n} diaphragmes ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
+        <v>Blanc SDR</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>Pastille blanc SDR</v>
+        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
+        <v>Pastille blanc SDR</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Assigner un profil</v>
+        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Aucun — selon ce qu’indique le fichier</v>
+        <v>Assigner un profil</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Profil intégré ({n} o)</v>
+        <v>Aucun — selon ce qu’indique le fichier</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>Profils HDR du pool</v>
+        <v>Profil intégré ({n} o)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Profil</v>
+        <v>Profils HDR du pool</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>profil intégré</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Chemin du moteur couleur</v>
+        <v>profil intégré</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>Chemin HDR, courbe de gain appliquée</v>
+        <v>Chemin du moteur couleur</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>Chemin HDR, sans courbe de gain</v>
+        <v>Chemin HDR, courbe de gain appliquée</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>AToB0 précalculé — pas le chemin HDR</v>
+        <v>Chemin HDR, sans courbe de gain</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Transfert</v>
+        <v>AToB0 précalculé — pas le chemin HDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>Blanc de référence HDR</v>
+        <v>Transfert</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Réserve cible</v>
+        <v>Blanc de référence HDR</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Courbe de gain (HAGC)</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Repli SDR précalculé (AToB0)</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>Application du profil…</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
+        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>Profils HDR</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Transfert linéaire</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Transfert non linéaire (PQ, HLG)</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Réserve de l’écran</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Référence</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Sans changement</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Identifier les écrans</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Événements d’affichage</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Plage complète</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Plage réduite</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>RAPPORT</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
+        <v>Détails de l’image</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>sans limite</v>
+        <v>indisponible — le navigateur rend cette image et ne peut pas la plafonner à un pic donné</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>limite {n} diaphragmes ({r}×)</v>
+        <v>indisponible — cette sortie n’affiche rien au-delà du blanc SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>Blanc SDR</v>
+        <v>indisponible — le pic de cet écran est inconnu</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
+        <v>Zoom avant</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>Pastille blanc SDR</v>
+        <v>Zoom arrière</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
+        <v>Ajuster l’image</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Assigner un profil</v>
+        <v>Pixels réels (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Aucun — selon ce qu’indique le fichier</v>
+        <v>Glisser pour déplacer · Ctrl+molette pour zoomer · double-clic pour réinitialiser</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Profil intégré ({n} o)</v>
+        <v>Glisser pour redimensionner la zone d’image ; double-clic pour revenir à la taille par défaut</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>Profils HDR du pool</v>
+        <v>Vue de l’image</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Profil</v>
+        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>profil intégré</v>
+        <v>sans limite</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Chemin du moteur couleur</v>
+        <v>limite {n} diaphragmes ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>Chemin HDR, courbe de gain appliquée</v>
+        <v>Blanc SDR</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>Chemin HDR, sans courbe de gain</v>
+        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>AToB0 précalculé — pas le chemin HDR</v>
+        <v>Pastille blanc SDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Transfert</v>
+        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>Blanc de référence HDR</v>
+        <v>Assigner un profil</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Réserve cible</v>
+        <v>Aucun — selon ce qu’indique le fichier</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
+        <v>Profil intégré ({n} o)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tone mapping</v>
+        <v>Profils HDR du pool</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Courbe de gain (HAGC)</v>
+        <v>profil intégré</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Repli SDR précalculé (AToB0)</v>
+        <v>Chemin du moteur couleur</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
+        <v>Chemin HDR, courbe de gain appliquée</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>Application du profil…</v>
+        <v>Chemin HDR, sans courbe de gain</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
+        <v>AToB0 précalculé — pas le chemin HDR</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
+        <v>Transfert</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
+        <v>Blanc de référence HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Profils HDR</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Transfert linéaire</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Transfert non linéaire (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Référence</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Sans changement</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Identifier les écrans</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Événements d’affichage</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Primaires de couleur</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Coefficients de matrice</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Plage complète</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Plage réduite</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>RAPPORT</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>ÉCHEC</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>contrôles</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>S’abonner</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Fermer</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>Adresse e-mail</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>vous@exemple.com</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(facultatif)</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Annuler</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>S’abonner</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Fermer</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Erreur :</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>Convertir en XML</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>Convertir en JSON</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>Convertir en ICC</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>Conversion en XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>ID du profil</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Nom de balise</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Décalage</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Taille</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Rembourrage</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Type</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Tableau de {type}</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>octets</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>Le profil est valide</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>État de validation inconnu</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Valide</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Avertissement</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Erreur</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Inconnu</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Réussi</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Échec</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Détail de validation</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Déclenché par</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Champ</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Valeur actuelle</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Requis : 0</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Attendu : {value}</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>Non valide</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Fermer</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>indentation</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>trier les clés</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Aperçu via le moteur couleur</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Tel que créé (base {h} diaphs, sans gain)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Mappé pour {h} diaphs</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>blanc de référence</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>pic de l’écran</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Aperçu indisponible : {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Gain pour toutes les marges</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Marge de l’écran (diaphs)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Gain (diaphs)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbe du tag</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Sans changement</v>
+        <v>Curseur</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Entrée = pic de l’écran</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Courbes de tons gris par marge</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Identifier les écrans</v>
+        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>{h} diaphs</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>{h} diaphs (base)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>À {h} diaphs (curseur)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Événements d’affichage</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Plage complète</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Plage réduite</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>RAPPORT</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>ÉCHEC</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>contrôles</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>Outil de profil ICC</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>S’abonner</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Fermer</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>Adresse e-mail</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>vous@exemple.com</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(facultatif)</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Annuler</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>S’abonner</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Fermer</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Avis de confidentialité</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Erreur :</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>Convertir en XML</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>Convertir en JSON</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>Convertir en ICC</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>Conversion en XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>Charger un profil ICC</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>ID du profil</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Nom de balise</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Décalage</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Taille</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Rembourrage</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Type</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Tableau de {type}</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>octets</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>Le profil est valide</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>État de validation inconnu</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Valide</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Avertissement</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Erreur</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Inconnu</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Réussi</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Échec</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Détail de validation</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Déclenché par</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Champ</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Valeur actuelle</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Requis : 0</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Attendu : {value}</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>Non valide</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Fermer</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>indentation</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>trier les clés</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Inconnu</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Réussi</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Échec</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Voir dans le contexte</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Détail de validation</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Déclenché par</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Champ</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Valeur actuelle</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Requis : 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Attendu : {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>Non valide</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Fermer</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>Chargement de l’éditeur XML…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>Chargement de l’éditeur JSON…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Réserve cible</v>
+        <v>Valeurs linéaires</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
+        <v>Fichier 1,0 = blanc de référence HDR</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tone mapping</v>
+        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>Les fichiers OpenEXR et Radiance HDR placent par convention le blanc SDR à 1,0, alors qu’un transfert ICC linéaire lit 1,0 comme 1 cd/m². Par défaut, le fichier est mis à l’échelle pour que son 1,0 tombe sur le blanc de référence HDR du profil.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Courbe de gain (HAGC)</v>
+        <v>Échelle d’entrée</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Repli SDR précalculé (AToB0)</v>
+        <v>×{w} — fichier 1,0 = blanc de référence</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
+        <v>aucune — fichier 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>Application du profil…</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>Profils HDR</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Transfert linéaire</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Transfert non linéaire (PQ, HLG)</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Référence</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Aperçu via le moteur couleur</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Tel que créé (base {h} diaphs, sans gain)</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Mappé pour {h} diaphs</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>blanc de référence</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>pic de l’écran</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Aperçu indisponible : {why}</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
+        <v>Aperçu via le moteur couleur</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Gain pour toutes les marges</v>
+        <v>Tel que créé (base {h} diaphs, sans gain)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
+        <v>Mappé pour {h} diaphs</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
+        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Marge de l’écran (diaphs)</v>
+        <v>blanc de référence</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Gain (diaphs)</v>
+        <v>pic de l’écran</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Courbe du tag</v>
+        <v>Aperçu indisponible : {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Base</v>
+        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Curseur</v>
+        <v>Gain pour toutes les marges</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Entrée = pic de l’écran</v>
+        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Courbes de tons gris par marge</v>
+        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
+        <v>Marge de l’écran (diaphs)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
+        <v>Gain (diaphs)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} diaphs</v>
+        <v>Courbe du tag</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} diaphs (base)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>À {h} diaphs (curseur)</v>
+        <v>Curseur</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>Entrée = pic de l’écran</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Courbes de tons gris par marge</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>{h} diaphs</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>{h} diaphs (base)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>À {h} diaphs (curseur)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Sans changement</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Identifier les écrans</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Événements d’affichage</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Primaires de couleur</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Coefficients de matrice</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Plage complète</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Plage réduite</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>RAPPORT</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>ÉCHEC</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>contrôles</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>Outil de profil ICC</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>S’abonner</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Fermer</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>Adresse e-mail</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>vous@exemple.com</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(facultatif)</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Annuler</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>S’abonner</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Fermer</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Avis de confidentialité</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Erreur :</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>Convertir en XML</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>Convertir en JSON</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>Convertir en ICC</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>Conversion en XML…</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>ID du profil</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Nom de balise</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Décalage</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Taille</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Rembourrage</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Type</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Tableau de {type}</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Aucun contenu)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>octets</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>Le profil est valide</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>État de validation inconnu</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Valide</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Avertissement</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Erreur</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Réussi</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Échec</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Détail de validation</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Déclenché par</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Champ</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Valeur actuelle</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Requis : 0</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Attendu : {value}</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>Non valide</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Fermer</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>indentation</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>trier les clés</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● modifications XML non enregistrées</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -4662,7 +4662,7 @@
         <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Tone mapping</v>
+        <v>Mappage des tons</v>
       </c>
     </row>
     <row r="533">

--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>Décodage…</v>
+        <v>Ce fichier fait {size} Mo ; l’onglet HDR ouvre les images jusqu’à {max} Mo.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Plage dynamique</v>
+        <v>Impossible d’appliquer le profil :</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
+        <v>Impossible de dessiner l’image :</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
+        <v>(ces primaires ne définissent pas d’espace colorimétrique — ignorées, Rec. 709 utilisé)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>ce navigateur le décode</v>
+        <v>le profil d’un JPEG XL est compressé dans le flux de code, que profiletool ne décompresse pas encore</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>ce navigateur ne le décode pas</v>
+        <v>Décodage…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
+        <v>Plage dynamique</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
+        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>reporté à une version ultérieure</v>
+        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
+        <v>ce navigateur le décode</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
+        <v>ce navigateur ne le décode pas</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
+        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
+        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
+        <v>reporté à une version ultérieure</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>format inconnu</v>
+        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} sous {os}</v>
+        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · écran HDR détecté</v>
+        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · écran SDR</v>
+        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
+        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
+        <v>format inconnu</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Pic de l’écran</v>
+        <v>{browser} sous {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
+        <v>{name} · écran HDR détecté</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — écran SDR</v>
+        <v>{name} · écran SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>inconnu</v>
+        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
+        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
+        <v>Pic de l’écran</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
+        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>Adapter à l’écran</v>
+        <v>1× — écran SDR</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Détails de l’image</v>
+        <v>inconnu</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>indisponible — le navigateur rend cette image et ne peut pas la plafonner à un pic donné</v>
+        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>indisponible — cette sortie n’affiche rien au-delà du blanc SDR</v>
+        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>indisponible — le pic de cet écran est inconnu</v>
+        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Zoom avant</v>
+        <v>Adapter à l’écran</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Zoom arrière</v>
+        <v>Détails de l’image</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Ajuster l’image</v>
+        <v>indisponible — le navigateur rend cette image et ne peut pas la plafonner à un pic donné</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Pixels réels (1:1)</v>
+        <v>indisponible — cette sortie n’affiche rien au-delà du blanc SDR</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Glisser pour déplacer · Ctrl+molette pour zoomer · double-clic pour réinitialiser</v>
+        <v>indisponible — le pic de cet écran est inconnu</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Glisser pour redimensionner la zone d’image ; double-clic pour revenir à la taille par défaut</v>
+        <v>Zoom avant</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Vue de l’image</v>
+        <v>Zoom arrière</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
+        <v>Ajuster l’image</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>sans limite</v>
+        <v>Pixels réels (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>limite {n} diaphragmes ({r}×)</v>
+        <v>Glisser pour déplacer · Ctrl+molette pour zoomer · double-clic pour réinitialiser</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>Blanc SDR</v>
+        <v>Glisser pour redimensionner la zone d’image ; double-clic pour revenir à la taille par défaut</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
+        <v>Vue de l’image</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>Pastille blanc SDR</v>
+        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
+        <v>sans limite</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Assigner un profil</v>
+        <v>limite {n} diaphragmes ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Aucun — selon ce qu’indique le fichier</v>
+        <v>Blanc SDR</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Profil intégré ({n} o)</v>
+        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>Profils HDR du pool</v>
+        <v>Pastille blanc SDR</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Profil</v>
+        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>profil intégré</v>
+        <v>Assigner un profil</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Chemin du moteur couleur</v>
+        <v>Aucun — selon ce qu’indique le fichier</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>Chemin HDR, courbe de gain appliquée</v>
+        <v>Profil intégré ({n} o)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>Chemin HDR, sans courbe de gain</v>
+        <v>Profils HDR du pool</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>AToB0 précalculé — pas le chemin HDR</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Transfert</v>
+        <v>profil intégré</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>Blanc de référence HDR</v>
+        <v>Chemin du moteur couleur</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Valeurs linéaires</v>
+        <v>Chemin HDR, courbe de gain appliquée</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>Fichier 1,0 = blanc de référence HDR</v>
+        <v>Chemin HDR, sans courbe de gain</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>AToB0 précalculé — pas le chemin HDR</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Les fichiers OpenEXR et Radiance HDR placent par convention le blanc SDR à 1,0, alors qu’un transfert ICC linéaire lit 1,0 comme 1 cd/m². Par défaut, le fichier est mis à l’échelle pour que son 1,0 tombe sur le blanc de référence HDR du profil.</v>
+        <v>Transfert</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Échelle d’entrée</v>
+        <v>Blanc de référence HDR</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — fichier 1,0 = blanc de référence</v>
+        <v>Valeurs linéaires</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>aucune — fichier 1,0 = 1 cd/m²</v>
+        <v>Fichier 1,0 = blanc de référence HDR</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Réserve cible</v>
+        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
+        <v>Les fichiers OpenEXR et Radiance HDR placent par convention le blanc SDR à 1,0, alors qu’un transfert ICC linéaire lit 1,0 comme 1 cd/m². Par défaut, le fichier est mis à l’échelle pour que son 1,0 tombe sur le blanc de référence HDR du profil.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Mappage des tons</v>
+        <v>Échelle d’entrée</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>×{w} — fichier 1,0 = blanc de référence</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Courbe de gain (HAGC)</v>
+        <v>aucune — fichier 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Repli SDR précalculé (AToB0)</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>Application du profil…</v>
+        <v>Mappage des tons</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>Profils HDR</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Transfert linéaire</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Transfert non linéaire (PQ, HLG)</v>
+        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Réserve de l’écran</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Référence</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Aperçu via le moteur couleur</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Tel que créé (base {h} diaphs, sans gain)</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Mappé pour {h} diaphs</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>blanc de référence</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>pic de l’écran</v>
+        <v>Aperçu via le moteur couleur</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Aperçu indisponible : {why}</v>
+        <v>Tel que créé (base {h} diaphs, sans gain)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
+        <v>Mappé pour {h} diaphs</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Gain pour toutes les marges</v>
+        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
+        <v>blanc de référence</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
+        <v>pic de l’écran</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Marge de l’écran (diaphs)</v>
+        <v>Aperçu indisponible : {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Gain (diaphs)</v>
+        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Courbe du tag</v>
+        <v>Gain pour toutes les marges</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Base</v>
+        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Curseur</v>
+        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrée = pic de l’écran</v>
+        <v>Marge de l’écran (diaphs)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Courbes de tons gris par marge</v>
+        <v>Gain (diaphs)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
+        <v>Courbe du tag</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} diaphs</v>
+        <v>Curseur</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} diaphs (base)</v>
+        <v>Entrée = pic de l’écran</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>À {h} diaphs (curseur)</v>
+        <v>Courbes de tons gris par marge</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>{h} diaphs</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>{h} diaphs (base)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>À {h} diaphs (curseur)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Sans changement</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Identifier les écrans</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Événements d’affichage</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Primaires de couleur</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Plage complète</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Plage réduite</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>RAPPORT</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>ÉCHEC</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>contrôles</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>Outil de profil ICC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>S’abonner</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Fermer</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Adresse e-mail</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>vous@exemple.com</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(facultatif)</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Annuler</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>S’abonner</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Fermer</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Erreur :</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>Convertir en XML</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>Convertir en JSON</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Convertir en ICC</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Conversion en XML…</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>ID du profil</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Nom de balise</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Décalage</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Taille</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Rembourrage</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Tableau de {type}</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>octets</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>Le profil est valide</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>État de validation inconnu</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Valide</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Avertissement</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Erreur</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Inconnu</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Réussi</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Échec</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Détail de validation</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Déclenché par</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Champ</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Valeur actuelle</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Requis : 0</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Attendu : {value}</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>Non valide</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Fermer</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>indentation</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>trier les clés</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● modifications JSON non enregistrées</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>indentation</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC sous Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC et JPEG XL sous Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et téléchargé.</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et ouvert ; rien n’est téléchargé tant que vous ne cliquez pas sur Enregistrer le profil ICC.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Trier par nom</v>
+        <v>Touchez pour sélectionner, puis touchez un onglet pour envoyer.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nouveau profil depuis .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et ouvert ; rien n’est téléchargé tant que vous ne cliquez pas sur Enregistrer le profil ICC.</v>
+        <v>Nouveau profil depuis .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Choisir un fichier .cube</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et ouvert ; rien n’est téléchargé tant que vous ne cliquez pas sur Enregistrer le profil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Choisir un fichier .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>ou déposez-le ici, ou collez ci-dessous</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Annuler</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Créer le DeviceLink</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Création…</v>
+        <v>Créer le DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparer</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Lier</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spectral</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Retirer</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intention de rendu</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Enveloppe</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Fil de fer</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Numéros des axes</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacité</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Couleur</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Uni</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Par valeur</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Par teinte</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Plateau tournant</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbite</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Roulis</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Construction du gamut…</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>pas de gamut</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Afficher / masquer</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plan</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Liaison</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Affichage RVB V5</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nom du profil</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Créer</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Création…</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Pipeline de liaison</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Terminé</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Vérification de l'image…</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformer l'image</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformation…</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Déposez des profils pour démarrer la chaîne</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>supprimé</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Déplacer plus tôt</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Déplacer plus tard</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Déplacer vers le haut</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Déplacer vers le bas</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intention de rendu (tout)</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intention de rendu pour cette transformation</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Les transformations utilisent des intentions de rendu différentes</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Chaîne</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>La chaîne n'a pas pu être analysée.</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Vérification de la chaîne…</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La chaîne ne se connecte pas ({detail}).</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrigez la chaîne avant de traiter des images</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Effacer</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Créer un DeviceLink</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nom du DeviceLink</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Création…</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Créez une chaîne pour traiter des images</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Image transformée enregistrée.</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Fichier de données trop volumineux.</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformer les données</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformation…</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Préférer</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observateur</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Illuminant</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrer {n} doublon(s)</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>médiane</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>moyenne</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>échantillons</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} doublons</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Résultat de la transformation</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} échantillons</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Enregistrer sous</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Enregistrer</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverser la transformation</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inversion…</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverser</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>dernière étape</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>première étape</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Données en {in} → recherche {out}</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Coût ΔE</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Cette image contient un profil ICC intégré.</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extraire et ajouter à la chaîne</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extraction…</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Ignorer</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Options de sortie de l'image</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Encodage</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Identique à la source</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flottant (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compression</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Aucune</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planaire</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Entrelacé</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Séparé</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolation CMM</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tétraédrique</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linéaire</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Intégrer le profil ICC</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembler un TIFF spectral</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Assembler et enregistrer</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Assemblage…</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n} canaux assemblés.</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Annuler</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>ou</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Choisir un fichier</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>En-tête</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Balises</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validation</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analyse</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intention de rendu</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% encre</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* en sortie (tonalité)</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* en sortie (tonalité)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimétrie des extrêmes</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
+        <v>Colorimétrie des extrêmes</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
+        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relative</v>
+        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolue</v>
+        <v>Relative</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Point blanc</v>
+        <v>Absolue</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Point noir</v>
+        <v>Point blanc</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Encrage au point noir</v>
+        <v>Point noir</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Encrage au point noir</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
+        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Aplat et chroma maximal</v>
+        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
+        <v>Aplat et chroma maximal</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Teinte</v>
+        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Aplat</v>
+        <v>Teinte</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* max</v>
+        <v>Aplat</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>À l’encrage</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
+        <v>À l’encrage</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Utilisation d’encre dans les ombres</v>
+        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
+        <v>Utilisation d’encre dans les ombres</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plan à L* constante</v>
+        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>avec compensation du point noir depuis</v>
+        <v>Plan à L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position le long du trajet</v>
+        <v>avec compensation du point noir depuis</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Trajet</v>
+        <v>Position le long du trajet</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Chemins d’encrage primaire par le neutre</v>
+        <v>Trajet</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Trois chemins dans le gamut — cyan→rouge, magenta→vert, jaune→bleu — chacun passant par l’axe neutre à la clarté médiane de ses extrémités, à travers la table B2A sélectionnée. Chaque échantillon est dans le gamut, donc contrairement aux chemins d’ombre, toute rupture ou inversion d’un colorant traduit un défaut de régularité de la CLUT plutôt qu’un artefact de mappage de gamut.</v>
+        <v>Chemins d’encrage primaire par le neutre</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Les chemins d’encrage primaire ne sont disponibles que pour les profils de sortie (imprimante).</v>
+        <v>Trois chemins dans le gamut — cyan→rouge, magenta→vert, jaune→bleu — chacun passant par l’axe neutre à la clarté médiane de ses extrémités, à travers la table B2A sélectionnée. Chaque échantillon est dans le gamut, donc contrairement aux chemins d’ombre, toute rupture ou inversion d’un colorant traduit un défaut de régularité de la CLUT plutôt qu’un artefact de mappage de gamut.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position le long du chemin (neutre au milieu)</v>
+        <v>Les chemins d’encrage primaire ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensation du point noir appliquée pour cette intention.</v>
+        <v>Position le long du chemin (neutre au milieu)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistiques d’utilisation d’encre</v>
+        <v>Compensation du point noir appliquée pour cette intention.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>La quantité de chaque colorant déposée par le profil, en somme et en part du total — la signature de consommation d’encre de la séparation.</v>
+        <v>Statistiques d’utilisation d’encre</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Les statistiques d’utilisation d’encre ne sont disponibles que pour les profils de sortie (imprimante).</v>
+        <v>La quantité de chaque colorant déposée par le profil, en somme et en part du total — la signature de consommation d’encre de la séparation.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Axe neutre</v>
+        <v>Les statistiques d’utilisation d’encre ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Couverture moyenne</v>
+        <v>Axe neutre</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Part d’encre</v>
+        <v>Couverture moyenne</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La part d’encre est l’empreinte de la construction du neutre — la fraction de chaque colorant dans le total d’encre déposée, indépendamment du nombre d’échantillons.</v>
+        <v>Part d’encre</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Points dans le gamut</v>
+        <v>La part d’encre est l’empreinte de la construction du neutre — la fraction de chaque colorant dans le total d’encre déposée, indépendamment du nombre d’échantillons.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>L’utilisation d’encre sur toutes les couleurs du gamut nécessite la frontière de gamut côté B2A, pas encore implémentée — à venir.</v>
+        <v>Points dans le gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Aucune donnée de colorant à résumer.</v>
+        <v>L’utilisation d’encre sur toutes les couleurs du gamut nécessite la frontière de gamut côté B2A, pas encore implémentée — à venir.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Sélectionnez une table B2A (PCS→périphérique) ci-dessous pour afficher aussi une image de couverture d’encre en niveaux de gris pour chaque colorant.</v>
+        <v>Aucune donnée de colorant à résumer.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Couverture d’encre de chaque colorant sur la même grille (plus sombre = plus d’encre).</v>
+        <v>Sélectionnez une table B2A (PCS→périphérique) ci-dessous pour afficher aussi une image de couverture d’encre en niveaux de gris pour chaque colorant.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Couverture d’encre de chaque colorant sur la même grille (plus sombre = plus d’encre).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Jaune</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rouge</v>
+        <v>Jaune</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Vert</v>
+        <v>Rouge</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Bleu</v>
+        <v>Vert</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Noir</v>
+        <v>Bleu</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptif</v>
+        <v>Noir</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturation</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Statistiques du profil</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intention de rendu</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>moyenne</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyse en cours…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analyse</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Tracé</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Sortie brute</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Courbes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Courbes de sortie</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Image CLUT</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Image de gamut</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Chromaticité</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Nuage de points</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Table de la courbe</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tables</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Données</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Évaluer</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Chargement…</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrée</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Sortie</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Virgule flottante</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Point de grille</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalisé</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Lisible</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Appareil → PCS</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Appareil</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Chargement…</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sécurité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformité</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualité</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Points de code</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Courbe de gain</v>
+        <v>Points de code</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Environnement</v>
+        <v>Courbe de gain</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>Affichage du repli SDR</v>
+        <v>Environnement</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>Profil HDR dans la chaîne</v>
+        <v>Affichage du repli SDR</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Les transformations via un profil HDR utilisent son AToB0Tag — le rendu SDR figé exigé par la clause 8.10.6 — car la clause 8.10.1 ne lui laisse aucune balise TRC. Le résultat est ce repli, pas un comportement HDR.</v>
+        <v>Profil HDR dans la chaîne</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Ce sont des profils HDR, sans balises TRC : le gamut est donc construit à partir de l’AToB0Tag, le rendu SDR figé qu’exige la clause 8.10.6 pour les consommateurs sans traitement HDR. Ce n’est pas le gamut HDR du profil, qui ne peut être tracé dans un PCS borné.</v>
+        <v>Les transformations via un profil HDR utilisent son AToB0Tag — le rendu SDR figé exigé par la clause 8.10.6 — car la clause 8.10.1 ne lui laisse aucune balise TRC. Le résultat est ce repli, pas un comportement HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Détection…</v>
+        <v>Ce sont des profils HDR, sans balises TRC : le gamut est donc construit à partir de l’AToB0Tag, le rendu SDR figé qu’exige la clause 8.10.6 pour les consommateurs sans traitement HDR. Ce n’est pas le gamut HDR du profil, qui ne peut être tracé dans un PCS borné.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>Détection de l’environnement impossible.</v>
+        <v>Détection…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>Écran HDR</v>
+        <v>Détection de l’environnement impossible.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Gamut étendu</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>Chemin canvas HDR</v>
+        <v>Gamut étendu</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRVB</v>
+        <v>Chemin canvas HDR</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>aucun</v>
+        <v>sRVB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>oui</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>non</v>
+        <v>oui</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>non communiqué</v>
+        <v>non</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Format</v>
+        <v>non communiqué</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Inspecter</v>
+        <v>Format</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Afficher</v>
+        <v>Inspecter</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Afficher</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Lire le profil ICC intégré — aucun codec requis</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Afficher les pixels</v>
+        <v>Lire le profil ICC intégré — aucun codec requis</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Rendu plus lumineux que le blanc</v>
+        <v>Afficher les pixels</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Décodé par profiletool, donc indépendant du navigateur</v>
+        <v>Rendu plus lumineux que le blanc</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Ce navigateur n’a pas indiqué la réserve HDR de l’écran, seulement si un chemin HDR existe.</v>
+        <v>Décodé par profiletool, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Options du navigateur</v>
+        <v>Ce navigateur n’a pas indiqué la réserve HDR de l’écran, seulement si un chemin HDR existe.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>activée</v>
+        <v>Options du navigateur</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>non activée</v>
+        <v>activée</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>impossible à détecter ici</v>
+        <v>non activée</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Nécessaire au rendu HDR dans ce navigateur : sans WebGPU, le canvas HDR est la seule voie. L’inspection des profils fonctionne sans.</v>
+        <v>impossible à détecter ici</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Facultatif : le HDR peut passer par WebGPU, mais ceci ajoute la voie canvas HDR et permet à profiletool de lire la vraie réserve HDR de l’écran.</v>
+        <v>Nécessaire au rendu HDR dans ce navigateur : sans WebGPU, le canvas HDR est la seule voie. L’inspection des profils fonctionne sans.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Les pages web ne peuvent pas ouvrir les pages d’options. Collez ceci dans la barre d’adresse, choisissez Enabled, puis relancez le navigateur.</v>
+        <v>Facultatif : le HDR peut passer par WebGPU, mais ceci ajoute la voie canvas HDR et permet à profiletool de lire la vraie réserve HDR de l’écran.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Copier</v>
+        <v>Les pages web ne peuvent pas ouvrir les pages d’options. Collez ceci dans la barre d’adresse, choisissez Enabled, puis relancez le navigateur.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Copié</v>
+        <v>Copier</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>Échec de la copie — sélectionnez l’adresse et copiez-la.</v>
+        <v>Copié</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Rapport de pixels</v>
+        <v>Échec de la copie — sélectionnez l’adresse et copiez-la.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Écran actuel</v>
+        <v>Rapport de pixels</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>sans nom</v>
+        <v>Écran actuel</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>principal</v>
+        <v>sans nom</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>intégré</v>
+        <v>principal</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>Réserve HDR</v>
+        <v>intégré</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>non exposée par ce navigateur</v>
+        <v>Réserve HDR</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium l’exprime en diaphragmes : log₂ de la luminance maximale de l’écran ÷ son niveau de blanc SDR. Sous Windows, la valeur n’est actualisée que lorsque Chrome relit l’écran — fenêtre déplacée vers un autre écran ou Chrome réactivé — et non lors d’un changement de luminosité.</v>
+        <v>non exposée par ce navigateur</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} diaphragmes (≈{ratio}× le blanc SDR)</v>
+        <v>Chromium l’exprime en diaphragmes : log₂ de la luminance maximale de l’écran ÷ son niveau de blanc SDR. Sous Windows, la valeur n’est actualisée que lorsque Chrome relit l’écran — fenêtre déplacée vers un autre écran ou Chrome réactivé — et non lors d’un changement de luminosité.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} diaphragmes (≈{ratio}× le blanc SDR)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Gain pour une réserve d’affichage</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Affichez une image HDR sur cet écran. Les fichiers que le navigateur sait décoder sont affichés par le navigateur lui-même ; OpenEXR et Radiance HDR sont décodés et rendus par profiletool.</v>
+        <v>Gain pour une réserve d’affichage</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>Déposez une image HDR ici, ou cliquez pour en choisir une</v>
+        <v>Affichez une image HDR sur cet écran. Les fichiers que le navigateur sait décoder sont affichés par le navigateur lui-même ; OpenEXR et Radiance HDR sont décodés et rendus par profiletool.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC et JPEG XL sous Safari.</v>
+        <v>Déposez une image HDR ici, ou cliquez pour en choisir une</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>En choisir une autre</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (y compris JPEG à gain map), PNG — et HEIC et JPEG XL sous Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Effacer</v>
+        <v>En choisir une autre</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Profil ICC intégré</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>aucun — OpenEXR indique la couleur par ses chromaticités</v>
+        <v>Profil ICC intégré</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>aucun — Radiance HDR indique la couleur par son en-tête PRIMARIES</v>
+        <v>aucun — OpenEXR indique la couleur par ses chromaticités</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>vérification…</v>
+        <v>aucun — Radiance HDR indique la couleur par son en-tête PRIMARIES</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>aucun</v>
+        <v>vérification…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Ouvrir dans l’onglet Profil</v>
+        <v>aucun</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Carte de gain</v>
+        <v>Ouvrir dans l’onglet Profil</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>détectée, non décodée</v>
+        <v>Carte de gain</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Ce n’est pas une image. Chargez les profils depuis le panneau Profils.</v>
+        <v>détectée, non décodée</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>Format d’image non reconnu par profiletool.</v>
+        <v>Ce n’est pas une image. Chargez les profils depuis le panneau Profils.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>Les pixels TIFF ne sont pas encore affichés ici : les navigateurs ne décodent pas le TIFF, et l’encodage HDR dans un TIFF 16 bits n’est pas encore décidé (phase 4.3). Son profil intégré peut être inspecté.</v>
+        <v>Format d’image non reconnu par profiletool.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>Impossible d’afficher cette image ici :</v>
+        <v>Les pixels TIFF ne sont pas encore affichés ici : les navigateurs ne décodent pas le TIFF, et l’encodage HDR dans un TIFF 16 bits n’est pas encore décidé (phase 4.3). Son profil intégré peut être inspecté.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>Son profil intégré peut toutefois être inspecté.</v>
+        <v>Impossible d’afficher cette image ici :</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Affiché par</v>
+        <v>Son profil intégré peut toutefois être inspecté.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>le navigateur</v>
+        <v>Affiché par</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>le navigateur</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>Écran HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>Les navigateurs ignorent le HDR signalé uniquement par un profil ICC intégré ; cette image peut donc paraître terne et plate.</v>
+        <v>Écran HDR</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Ce navigateur ne peut pas basculer une image entre SDR et HDR ; elle est affichée telle que le navigateur la rend.</v>
+        <v>Les navigateurs ignorent le HDR signalé uniquement par un profil ICC intégré ; cette image peut donc paraître terne et plate.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>Le navigateur n’a pas pu décoder cette image.</v>
+        <v>Ce navigateur ne peut pas basculer une image entre SDR et HDR ; elle est affichée telle que le navigateur la rend.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Sortie</v>
+        <v>Le navigateur n’a pas pu décoder cette image.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>Canevas HDR (float16)</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (plage étendue)</v>
+        <v>Canevas HDR (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>Canevas SDR (tone mapping)</v>
+        <v>WebGPU (plage étendue)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Taille</v>
+        <v>Canevas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Pixel le plus lumineux</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× le blanc SDR</v>
+        <v>Pixel le plus lumineux</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Chromaticités</v>
+        <v>{n}× le blanc SDR</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>non indiquées — Rec. 709 supposé</v>
+        <v>Chromaticités</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} n’est pas disponible ici ({why}) ; la sortie suivante est utilisée.</v>
+        <v>non indiquées — Rec. 709 supposé</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Cette sortie ne peut pas transporter de valeurs plus claires que le blanc ; le rendu SDR après tone mapping est affiché.</v>
+        <v>{from} n’est pas disponible ici ({why}) ; la sortie suivante est utilisée.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Exposition</v>
+        <v>Cette sortie ne peut pas transporter de valeurs plus claires que le blanc ; le rendu SDR après tone mapping est affiché.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} diaphragmes</v>
+        <v>Exposition</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>Décodage impossible :</v>
+        <v>{n} diaphragmes</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Ce fichier fait {size} Mo ; l’onglet HDR ouvre les images jusqu’à {max} Mo.</v>
+        <v>Décodage impossible :</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>Impossible d’appliquer le profil :</v>
+        <v>Ce fichier fait {size} Mo ; l’onglet HDR ouvre les images jusqu’à {max} Mo.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>Impossible de dessiner l’image :</v>
+        <v>Impossible d’appliquer le profil :</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(ces primaires ne définissent pas d’espace colorimétrique — ignorées, Rec. 709 utilisé)</v>
+        <v>Impossible de dessiner l’image :</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>le profil d’un JPEG XL est compressé dans le flux de code, que profiletool ne décompresse pas encore</v>
+        <v>(ces primaires ne définissent pas d’espace colorimétrique — ignorées, Rec. 709 utilisé)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>Décodage…</v>
+        <v>le profil d’un JPEG XL est compressé dans le flux de code, que profiletool ne décompresse pas encore</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Plage dynamique</v>
+        <v>Décodage…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
+        <v>Plage dynamique</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
+        <v>Ce navigateur ne propose que les deux extrêmes, pas de mélange.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>ce navigateur le décode</v>
+        <v>décodé par profiletool lui-même, donc indépendant du navigateur</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>ce navigateur ne le décode pas</v>
+        <v>ce navigateur le décode</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
+        <v>ce navigateur ne le décode pas</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
+        <v>l’affichage HEIC nécessite Safari ou un autre navigateur WebKit — Chrome et Firefox ne décodent le HEIC sur aucune plateforme, macOS compris</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>reporté à une version ultérieure</v>
+        <v>l’affichage JPEG XL nécessite Safari ; les autres navigateurs ne l’ont pas livré</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
+        <v>reporté à une version ultérieure</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
+        <v>cet écran ne signale aucun chemin HDR, le HDR est donc rendu en SDR après tone mapping</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
+        <v>ce navigateur n’expose aucun canevas HDR (canevas float16 ou WebGPU requis)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
+        <v>Firefox n’affiche aucune image HDR et ne lit aucune gain map ; le contenu HDR est affiché en SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
+        <v>l’inspection demande une analyse du conteneur, pas un codec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>format inconnu</v>
+        <v>un écran HDR et un canevas HDR sont tous deux disponibles</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} sous {os}</v>
+        <v>format inconnu</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · écran HDR détecté</v>
+        <v>{browser} sous {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · écran SDR</v>
+        <v>{name} · écran HDR détecté</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
+        <v>{name} · écran SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
+        <v>WebGPU a appliqué le tone mapping « {mode} » ; la sortie est donc limitée au SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Pic de l’écran</v>
+        <v>Ce navigateur n’indique pas le tone mapping WebGPU appliqué ; la sortie HDR n’est pas confirmée</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
+        <v>Pic de l’écran</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — écran SDR</v>
+        <v>{r}× le blanc SDR ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>inconnu</v>
+        <v>1× — écran SDR</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
+        <v>inconnu</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
+        <v>Cet écran ne signale pas de HDR ; le navigateur affiche donc cette image en SDR aux deux extrêmes.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
+        <v>Cet écran ne signale pas de HDR ; tout ce qui dépasse le blanc SDR est donc écrêté. « Adapter à l’écran » affiche plutôt le rendu après tone mapping.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>Adapter à l’écran</v>
+        <v>Cette image demande {img}× le blanc SDR, mais cet écran n’affiche que jusqu’à {disp}× ; les valeurs plus claires sont écrêtées. « Adapter à l’écran » les ramène progressivement vers le pic de l’écran.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Détails de l’image</v>
+        <v>Adapter à l’écran</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>indisponible — le navigateur rend cette image et ne peut pas la plafonner à un pic donné</v>
+        <v>Détails de l’image</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>indisponible — cette sortie n’affiche rien au-delà du blanc SDR</v>
+        <v>indisponible — le navigateur rend cette image et ne peut pas la plafonner à un pic donné</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>indisponible — le pic de cet écran est inconnu</v>
+        <v>indisponible — cette sortie n’affiche rien au-delà du blanc SDR</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Zoom avant</v>
+        <v>indisponible — le pic de cet écran est inconnu</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Zoom arrière</v>
+        <v>Zoom avant</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Ajuster l’image</v>
+        <v>Zoom arrière</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Pixels réels (1:1)</v>
+        <v>Ajuster l’image</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Glisser pour déplacer · Ctrl+molette pour zoomer · double-clic pour réinitialiser</v>
+        <v>Pixels réels (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Glisser pour redimensionner la zone d’image ; double-clic pour revenir à la taille par défaut</v>
+        <v>Glisser pour déplacer · Ctrl+molette pour zoomer · double-clic pour réinitialiser</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Vue de l’image</v>
+        <v>Glisser pour redimensionner la zone d’image ; double-clic pour revenir à la taille par défaut</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
+        <v>Vue de l’image</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>sans limite</v>
+        <v>Limite la luminosité au pic indiqué par cet écran. Sous Windows, cette valeur peut tarder à suivre les changements de luminosité.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>limite {n} diaphragmes ({r}×)</v>
+        <v>sans limite</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>Blanc SDR</v>
+        <v>limite {n} diaphragmes ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
+        <v>Blanc SDR</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>Pastille blanc SDR</v>
+        <v>Blanc SDR simple, pour comparaison. Sur un écran HDR, les hautes lumières HDR paraissent plus claires que lui.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
+        <v>Pastille blanc SDR</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Assigner un profil</v>
+        <v>Faites-la glisser pour la déplacer ; double-cliquez pour la remettre à côté de l’image.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Aucun — selon ce qu’indique le fichier</v>
+        <v>Assigner un profil</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Profil intégré ({n} o)</v>
+        <v>Aucun — selon ce qu’indique le fichier</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>Profils HDR du pool</v>
+        <v>Profil intégré ({n} o)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Profil</v>
+        <v>Profils HDR du pool</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>profil intégré</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Chemin du moteur couleur</v>
+        <v>profil intégré</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>Chemin HDR, courbe de gain appliquée</v>
+        <v>Chemin du moteur couleur</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>Chemin HDR, sans courbe de gain</v>
+        <v>Chemin HDR, courbe de gain appliquée</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>AToB0 précalculé — pas le chemin HDR</v>
+        <v>Chemin HDR, sans courbe de gain</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Transfert</v>
+        <v>AToB0 précalculé — pas le chemin HDR</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>Blanc de référence HDR</v>
+        <v>Transfert</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Valeurs linéaires</v>
+        <v>Blanc de référence HDR</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>Fichier 1,0 = blanc de référence HDR</v>
+        <v>Valeurs linéaires</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Fichier 1,0 = blanc de référence HDR</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Les fichiers OpenEXR et Radiance HDR placent par convention le blanc SDR à 1,0, alors qu’un transfert ICC linéaire lit 1,0 comme 1 cd/m². Par défaut, le fichier est mis à l’échelle pour que son 1,0 tombe sur le blanc de référence HDR du profil.</v>
+        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Échelle d’entrée</v>
+        <v>Les fichiers OpenEXR et Radiance HDR placent par convention le blanc SDR à 1,0, alors qu’un transfert ICC linéaire lit 1,0 comme 1 cd/m². Par défaut, le fichier est mis à l’échelle pour que son 1,0 tombe sur le blanc de référence HDR du profil.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — fichier 1,0 = blanc de référence</v>
+        <v>Échelle d’entrée</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>aucune — fichier 1,0 = 1 cd/m²</v>
+        <v>×{w} — fichier 1,0 = blanc de référence</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Réserve cible</v>
+        <v>aucune — fichier 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
+        <v>Réserve cible</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Mappage des tons</v>
+        <v>{r}× le blanc de référence ({n} diaphragmes)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>Mappage des tons</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Courbe de gain (HAGC)</v>
+        <v>Auto (classement de la clause 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Repli SDR précalculé (AToB0)</v>
+        <v>Courbe de gain (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
+        <v>Repli SDR précalculé (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>Application du profil…</v>
+        <v>Désactivé — comme un CMM antérieur à l’amendement</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
+        <v>Application du profil…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
+        <v>{format} contient de la lumière linéaire ; il faut un profil dont le transfert est Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
+        <v>Assigner un profil nécessite une image RVB à 3 canaux.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>Profils HDR</v>
+        <v>Pour interpréter ses valeurs, assignez un profil ci-dessus.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Transfert linéaire</v>
+        <v>Profils HDR</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Transfert non linéaire (PQ, HLG)</v>
+        <v>Transfert linéaire</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Transfert non linéaire (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>Profils HDR — transfert linéaire</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>Profils HDR — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Réserve de l’écran</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Référence</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Aperçu via le moteur couleur</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Tel que créé (base {h} diaphs, sans gain)</v>
+        <v>Aperçu via le moteur couleur</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Mappé pour {h} diaphs</v>
+        <v>Tel que créé (base {h} diaphs, sans gain)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
+        <v>Mappé pour {h} diaphs</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>blanc de référence</v>
+        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>pic de l’écran</v>
+        <v>blanc de référence</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Aperçu indisponible : {why}</v>
+        <v>pic de l’écran</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
+        <v>Aperçu indisponible : {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Gain pour toutes les marges</v>
+        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
+        <v>Gain pour toutes les marges</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
+        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Marge de l’écran (diaphs)</v>
+        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Gain (diaphs)</v>
+        <v>Marge de l’écran (diaphs)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Courbe du tag</v>
+        <v>Gain (diaphs)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Base</v>
+        <v>Courbe du tag</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Curseur</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Entrée = pic de l’écran</v>
+        <v>Curseur</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Courbes de tons gris par marge</v>
+        <v>Entrée = pic de l’écran</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
+        <v>Courbes de tons gris par marge</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
+        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} diaphs</v>
+        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} diaphs (base)</v>
+        <v>{h} diaphs</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>À {h} diaphs (curseur)</v>
+        <v>{h} diaphs (base)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>À {h} diaphs (curseur)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Sans changement</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Identifier les écrans</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Événements d’affichage</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Plage complète</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Plage réduite</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>RAPPORT</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Trier par nom</v>
+        <v>Touchez pour sélectionner, puis touchez un onglet pour envoyer.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Trier par nom</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nouveau profil depuis .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et ouvert ; rien n’est téléchargé tant que vous ne cliquez pas sur Enregistrer le profil ICC.</v>
+        <v>Nouveau profil depuis .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Choisir un fichier .cube</v>
+        <v>Créez un DeviceLink ICC à partir d’une LUT 3D .cube Adobe/Resolve. Le résultat est ajouté à votre pool et ouvert ; rien n’est téléchargé tant que vous ne cliquez pas sur Enregistrer le profil ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Choisir un fichier .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>ou déposez-le ici, ou collez ci-dessous</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Annuler</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Créer le DeviceLink</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Création…</v>
+        <v>Créer le DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profil</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Comparer</v>
+        <v>Profil</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Lier</v>
+        <v>Comparer</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spectral</v>
+        <v>Lier</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Faites glisser des profils du pool vers cet onglet</v>
+        <v>Spectral</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Retirer</v>
+        <v>Faites glisser des profils du pool vers cet onglet</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Aucun profil sélectionné</v>
+        <v>Retirer</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
+        <v>Aucun profil sélectionné</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Rien à comparer pour l’instant</v>
+        <v>Faites glisser un profil du pool vers l’onglet Profil pour l’inspecter.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
+        <v>Rien à comparer pour l’instant</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Comparaison de gamut</v>
+        <v>Faites glisser un ou plusieurs profils vers l’onglet Comparer.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
+        <v>Comparaison de gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intention de rendu</v>
+        <v>Les vues gamut 3D et coupe 2D arrivent ici. Accumulés :</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Enveloppe</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Fil de fer</v>
+        <v>Enveloppe</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Numéros des axes</v>
+        <v>Fil de fer</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacité</v>
+        <v>Numéros des axes</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Couleur</v>
+        <v>Opacité</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Uni</v>
+        <v>Couleur</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Par valeur</v>
+        <v>Uni</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Par teinte</v>
+        <v>Par valeur</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotation</v>
+        <v>Par teinte</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Plateau tournant</v>
+        <v>Rotation</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbite</v>
+        <v>Plateau tournant</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Vitesse de glissement</v>
+        <v>Orbite</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Roulis</v>
+        <v>Vitesse de glissement</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Vitesse de roulis</v>
+        <v>Roulis</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Construction du gamut…</v>
+        <v>Vitesse de roulis</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>pas de gamut</v>
+        <v>Construction du gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Afficher / masquer</v>
+        <v>pas de gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Enveloppe de gamut 3D</v>
+        <v>Afficher / masquer</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Coupe de gamut 2D</v>
+        <v>Enveloppe de gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Plan</v>
+        <v>Coupe de gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Plan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Liaison</v>
+        <v>Aucun des profils sélectionnés n’a de transformation périphérique→PCS permettant de dériver un gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
+        <v>Liaison</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
+        <v>La production de DeviceLink et les transformations multi-profils arriveront dans une phase ultérieure.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Créateur d’affichage V4</v>
+        <v>D’autres créateurs de liens (DeviceLink, …) arriveront ici.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
+        <v>Créateur d’affichage V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Affichage RVB V5</v>
+        <v>Faites glisser un profil d’affichage RVB V5 et un profil d’observateur V5 ici pour créer un profil d’affichage V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>déposez un profil d’affichage</v>
+        <v>Affichage RVB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Observateur V5 (PCC)</v>
+        <v>déposez un profil d’affichage</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>déposez un profil d’observateur</v>
+        <v>Observateur V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
+        <v>déposez un profil d’observateur</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Créer le profil d’affichage V4</v>
+        <v>Un profil qui n’est ni un affichage RVB V5 ni un observateur a été ignoré.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nom du profil</v>
+        <v>Créer le profil d’affichage V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Créer</v>
+        <v>Nom du profil</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Création…</v>
+        <v>Créer</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Pipeline de liaison</v>
+        <v>« {name} » créé — ajouté au pool et à cet onglet.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
+        <v>Pipeline de liaison</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Terminé</v>
+        <v>Créez une chaîne de profils, puis créez un DeviceLink, transformez une image ou transformez un jeu de données colorimétriques.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
+        <v>Terminé</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Vérification de l'image…</v>
+        <v>Déposez une image à transformer (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
+        <v>Vérification de l'image…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
+        <v>Format d'image non pris en charge (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Transformer l'image</v>
+        <v>Image trop grande ({mp} MP ; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Transformation…</v>
+        <v>Transformer l'image</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Déposez des profils pour démarrer la chaîne</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>supprimé</v>
+        <v>Déposez des profils pour démarrer la chaîne</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Déplacer plus tôt</v>
+        <v>supprimé</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Déplacer plus tard</v>
+        <v>Déplacer plus tôt</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Déplacer vers le haut</v>
+        <v>Déplacer plus tard</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Déplacer vers le bas</v>
+        <v>Déplacer vers le haut</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intention de rendu (tout)</v>
+        <v>Déplacer vers le bas</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intention de rendu pour cette transformation</v>
+        <v>Intention de rendu (tout)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Les transformations utilisent des intentions de rendu différentes</v>
+        <v>Intention de rendu pour cette transformation</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
+        <v>Les transformations utilisent des intentions de rendu différentes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
+        <v>Inverser le sens de la chaîne (inverse la transformation de tête, avec répercussion sur toute la chaîne)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Chaîne</v>
+        <v>Un profil de la chaîne a été supprimé de la réserve — retirez-le pour continuer.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>La chaîne n'a pas pu être analysée.</v>
+        <v>Chaîne</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Vérification de la chaîne…</v>
+        <v>La chaîne n'a pas pu être analysée.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La chaîne ne se connecte pas ({detail}).</v>
+        <v>Vérification de la chaîne…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
+        <v>La chaîne ne se connecte pas ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Corrigez la chaîne avant de traiter des images</v>
+        <v>Le profil {n} ne se connecte pas à l'étape précédente ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Effacer</v>
+        <v>Corrigez la chaîne avant de traiter des images</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Créer un DeviceLink</v>
+        <v>Effacer</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nom du DeviceLink</v>
+        <v>Créer un DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Création…</v>
+        <v>Nom du DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
+        <v>Création…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
+        <v>« {name} » créé — ajouté à la réserve et à cet onglet.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Créez une chaîne pour traiter des images</v>
+        <v>Déposez des images {src} à convertir en {dst} — les résultats se téléchargent, rien n'est stocké.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
+        <v>Créez une chaîne pour traiter des images</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Image transformée enregistrée.</v>
+        <v>Cette chaîne ne commence ni ne se termine dans un espace colorimétrique d'image</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
+        <v>Image transformée enregistrée.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossible de lire ce fichier.</v>
+        <v>Déposez un jeu de données colorimétriques (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>Fichier de données trop volumineux.</v>
+        <v>Impossible de lire ce fichier.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Transformer les données</v>
+        <v>Fichier de données trop volumineux.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Transformation…</v>
+        <v>Transformer les données</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Préférer</v>
+        <v>Transformation…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Observateur</v>
+        <v>Préférer</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Illuminant</v>
+        <v>Observateur</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtrer {n} doublon(s)</v>
+        <v>Condition</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>médiane</v>
+        <v>Filtrer {n} doublon(s)</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>moyenne</v>
+        <v>médiane</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>échantillons</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} doublons</v>
+        <v>échantillons</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Résultat de la transformation</v>
+        <v>{n} doublons</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} échantillons</v>
+        <v>Résultat de la transformation</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
+        <v>{src} → {dst} · {n} échantillons</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Enregistrer sous</v>
+        <v>Affichage des {shown} premiers sur {total} — Enregistrer les écrira tous.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Enregistrer</v>
+        <v>Enregistrer sous</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverser la transformation</v>
+        <v>Enregistrer</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inversion…</v>
+        <v>Inverser la transformation</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverser</v>
+        <v>Inversion…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>dernière étape</v>
+        <v>Inverser</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>première étape</v>
+        <v>dernière étape</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Données en {in} → recherche {out}</v>
+        <v>première étape</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
+        <v>Données en {in} → recherche {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
+        <v>L'inversion nécessite une chaîne de 2 à 3 profils</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Coût ΔE</v>
+        <v>Le jeu de données doit être en {in} ; la recherche inverse produit {out} ainsi qu'un coût d'inversibilité par échantillon.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Cette image contient un profil ICC intégré.</v>
+        <v>Coût ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Extraire et ajouter à la chaîne</v>
+        <v>Cette image contient un profil ICC intégré.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Extraction…</v>
+        <v>Extraire et ajouter à la chaîne</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Ignorer</v>
+        <v>Extraction…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
+        <v>Ignorer</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Options de sortie de l'image</v>
+        <v>Profil intégré extrait — ajouté à la réserve et placé en tête de chaîne.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Encodage</v>
+        <v>Options de sortie de l'image</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Identique à la source</v>
+        <v>Encodage</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bits</v>
+        <v>Identique à la source</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Flottant (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compression</v>
+        <v>Flottant (32 bits)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Aucune</v>
+        <v>Compression</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planaire</v>
+        <v>Aucune</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Entrelacé</v>
+        <v>Planaire</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Séparé</v>
+        <v>Entrelacé</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolation CMM</v>
+        <v>Séparé</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tétraédrique</v>
+        <v>Interpolation CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Linéaire</v>
+        <v>Tétraédrique</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Intégrer le profil ICC</v>
+        <v>Linéaire</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
+        <v>Intégrer le profil ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembler un TIFF spectral</v>
+        <v>L'encodage, la compression et la disposition planaire déterminent le TIFF enregistré. La sortie RGB/Gray reste en PNG sauf si une option réservée au TIFF (flottant, LZW/ZIP, séparé) est définie.</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
+        <v>Assembler un TIFF spectral</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
+        <v>Déposez des images spectrales monocanal dans l'ordre des canaux, puis assemblez-les en un seul TIFF multicanal.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Déposez les images spectrales ici (ou cliquez pour choisir)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Assembler et enregistrer</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Assemblage…</v>
+        <v>Assembler et enregistrer</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>{n} canaux assemblés.</v>
+        <v>Assemblage…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
+        <v>{n} canaux assemblés.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Annuler</v>
+        <v>Aucun de ces fichiers ne ressemble à une image (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} fichier(s) non chargé(s)</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
+        <v>{n} fichier(s) non chargé(s)</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Ces fichiers ne sont pas des profils ICC ; ils n’ont donc pas été ajoutés au pool :</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Déposez un profil ICC ici</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>ou</v>
+        <v>Déposez un profil ICC ici</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Choisir un fichier</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>Fichiers .icc et .icm</v>
+        <v>Choisir un fichier</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>En-tête</v>
+        <v>Fichiers .icc et .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Balises</v>
+        <v>En-tête</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Validation</v>
+        <v>Balises</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analyse</v>
+        <v>Validation</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Encrage de l’axe neutre</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
+        <v>Encrage de l’axe neutre</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Colorant déposé le long de l’axe neutre (a*=b*=0) à mesure que la clarté passe du blanc (L*=100) au noir (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
+        <v>L’encrage de l’axe neutre n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intention de rendu</v>
+        <v>Ce profil n’a pas de table B2A (PCS→périphérique) à échantillonner.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% encre</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* en sortie (tonalité)</v>
+        <v>% encre</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* en sortie (tonalité)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimétrie des extrêmes</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
+        <v>Colorimétrie des extrêmes</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
+        <v>Les extrémités de la plage de reproduction du profil : le blanc du support, le noir le plus dense qu’il imprimera, l’encre que ce noir coûte, et l’endroit où chaque teinte atteint son point le plus saturé.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relative</v>
+        <v>Le point blanc est la couleur à colorant nul — le support nu. Le point noir est obtenu en faisant passer le noir PCS (L*=0, a*=b*=0) par la table B2A sélectionnée pour obtenir l’encrage que le profil choisit pour le noir, puis en relisant cet encrage via A2B1. La couverture d’encre totale (TAC) est la somme de cet encrage. La colorimétrie absolue montre la couleur propre du support ; la relative la ramène à un blanc parfait.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Absolue</v>
+        <v>Relative</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Point blanc</v>
+        <v>Absolue</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Point noir</v>
+        <v>Point blanc</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Encrage au point noir</v>
+        <v>Point noir</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Encrage au point noir</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
+        <v>Ce profil n’a pas de balise de point blanc du média ; la colorimétrie absolue est donc indisponible.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Aplat et chroma maximal</v>
+        <v>La colorimétrie des extrêmes n’est disponible que pour les profils de sortie (imprimante) — elle suppose qu’un colorant nul correspond au support nu.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
+        <v>Aplat et chroma maximal</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Teinte</v>
+        <v>Où se situe chaque coin d’encre, et le point le plus chromatique sur le chemin. Mesuré via A2B1 : ces lignes ne changent donc pas avec l’intention de rendu ci-dessus. Sur un profil sain, les deux lignes coïncident ; si le chroma maximal survient avant l’aplat, l’encre ajoutée au-delà ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Aplat</v>
+        <v>Teinte</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* max</v>
+        <v>Aplat</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>À l’encrage</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
+        <v>À l’encrage</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Utilisation d’encre dans les ombres</v>
+        <v>Le chroma maximal est atteint avant l’aplat — au-delà, l’encre ne fait qu’assombrir.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
+        <v>Utilisation d’encre dans les ombres</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
+        <v>Quatre trajets rectilignes dans le plan a*b* à une clarté constante et délibérément sombre, passés par la table B2A sélectionnée. Tous les échantillons partagent la même L*, de sorte que tout saut brusque ou inversion d’un colorant provient uniquement du traitement de la teinte et du chroma — la signature d’un artefact de mappage de gamut dans les ombres.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Plan à L* constante</v>
+        <v>L’utilisation d’encre dans les ombres n’est disponible que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>avec compensation du point noir depuis</v>
+        <v>Plan à L* constante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Position le long du trajet</v>
+        <v>avec compensation du point noir depuis</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Trajet</v>
+        <v>Position le long du trajet</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Chemins d’encrage primaire par le neutre</v>
+        <v>Trajet</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Trois chemins dans le gamut — cyan→rouge, magenta→vert, jaune→bleu — chacun passant par l’axe neutre à la clarté médiane de ses extrémités, à travers la table B2A sélectionnée. Chaque échantillon est dans le gamut, donc contrairement aux chemins d’ombre, toute rupture ou inversion d’un colorant traduit un défaut de régularité de la CLUT plutôt qu’un artefact de mappage de gamut.</v>
+        <v>Chemins d’encrage primaire par le neutre</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>Les chemins d’encrage primaire ne sont disponibles que pour les profils de sortie (imprimante).</v>
+        <v>Trois chemins dans le gamut — cyan→rouge, magenta→vert, jaune→bleu — chacun passant par l’axe neutre à la clarté médiane de ses extrémités, à travers la table B2A sélectionnée. Chaque échantillon est dans le gamut, donc contrairement aux chemins d’ombre, toute rupture ou inversion d’un colorant traduit un défaut de régularité de la CLUT plutôt qu’un artefact de mappage de gamut.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Position le long du chemin (neutre au milieu)</v>
+        <v>Les chemins d’encrage primaire ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensation du point noir appliquée pour cette intention.</v>
+        <v>Position le long du chemin (neutre au milieu)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistiques d’utilisation d’encre</v>
+        <v>Compensation du point noir appliquée pour cette intention.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>La quantité de chaque colorant déposée par le profil, en somme et en part du total — la signature de consommation d’encre de la séparation.</v>
+        <v>Statistiques d’utilisation d’encre</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Les statistiques d’utilisation d’encre ne sont disponibles que pour les profils de sortie (imprimante).</v>
+        <v>La quantité de chaque colorant déposée par le profil, en somme et en part du total — la signature de consommation d’encre de la séparation.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Axe neutre</v>
+        <v>Les statistiques d’utilisation d’encre ne sont disponibles que pour les profils de sortie (imprimante).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Couverture moyenne</v>
+        <v>Axe neutre</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Part d’encre</v>
+        <v>Couverture moyenne</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La part d’encre est l’empreinte de la construction du neutre — la fraction de chaque colorant dans le total d’encre déposée, indépendamment du nombre d’échantillons.</v>
+        <v>Part d’encre</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Points dans le gamut</v>
+        <v>La part d’encre est l’empreinte de la construction du neutre — la fraction de chaque colorant dans le total d’encre déposée, indépendamment du nombre d’échantillons.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>L’utilisation d’encre sur toutes les couleurs du gamut nécessite la frontière de gamut côté B2A, pas encore implémentée — à venir.</v>
+        <v>Points dans le gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Aucune donnée de colorant à résumer.</v>
+        <v>L’utilisation d’encre sur toutes les couleurs du gamut nécessite la frontière de gamut côté B2A, pas encore implémentée — à venir.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Sélectionnez une table B2A (PCS→périphérique) ci-dessous pour afficher aussi une image de couverture d’encre en niveaux de gris pour chaque colorant.</v>
+        <v>Aucune donnée de colorant à résumer.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Couverture d’encre de chaque colorant sur la même grille (plus sombre = plus d’encre).</v>
+        <v>Sélectionnez une table B2A (PCS→périphérique) ci-dessous pour afficher aussi une image de couverture d’encre en niveaux de gris pour chaque colorant.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Cyan</v>
+        <v>Couverture d’encre de chaque colorant sur la même grille (plus sombre = plus d’encre).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Jaune</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rouge</v>
+        <v>Jaune</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Vert</v>
+        <v>Rouge</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Bleu</v>
+        <v>Vert</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Noir</v>
+        <v>Bleu</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Perceptif</v>
+        <v>Noir</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimétrique relatif</v>
+        <v>Perceptif</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturation</v>
+        <v>Colorimétrique relatif</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimétrique absolu</v>
+        <v>Saturation</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Statistiques du profil</v>
+        <v>Colorimétrique absolu</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
+        <v>Statistiques du profil</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
+        <v>Mesures globales du profil par intention de rendu : le volume de gamut délimité par la transformation périphérique→PCS (ΔE*ab³) et la précision de l’aller-retour B2A — ΔE*ab d’un aller-retour Lab → périphérique → Lab à travers le profil.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intention de rendu</v>
+        <v>Aucune CLUT périphérique↔PCS dans ce profil — les statistiques du profil ne s’appliquent pas (par exemple un profil d’affichage matrice/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intention de rendu</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE aller-retour</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
+        <v>ΔE aller-retour</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>moyenne</v>
+        <v>La frontière du gamut s’est effondrée ou était en grande partie indéfinie ; ce volume de gamut n’est pas fiable.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>moyenne</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analyse en cours…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analyse</v>
+        <v>Analyse en cours…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
+        <v>Analyse</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Tracé</v>
+        <v>Analyses de qualité à l’échelle du profil, dérivées de la transformation périphérique→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Sortie brute</v>
+        <v>Tracé</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Sortie brute</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Courbes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Courbes d’entrée</v>
+        <v>Courbes</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Courbes de sortie</v>
+        <v>Courbes d’entrée</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Image CLUT</v>
+        <v>Courbes de sortie</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Image de gamut</v>
+        <v>Image CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Chromaticité</v>
+        <v>Image de gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Nuage de points</v>
+        <v>Chromaticité</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Courbe de réponse tonale</v>
+        <v>Nuage de points</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Table de la courbe</v>
+        <v>Courbe de réponse tonale</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tables</v>
+        <v>Table de la courbe</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Données</v>
+        <v>Tables</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Évaluer</v>
+        <v>Données</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Chargement…</v>
+        <v>Évaluer</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Entrée</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Sortie</v>
+        <v>Entrée</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Virgule flottante</v>
+        <v>Sortie</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Point de grille</v>
+        <v>Virgule flottante</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalisé</v>
+        <v>Point de grille</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Lisible</v>
+        <v>Normalisé</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Appareil → PCS</v>
+        <v>Lisible</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Appareil</v>
+        <v>Appareil → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Aucune grille CLUT</v>
+        <v>PCS → Appareil</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Chargement…</v>
+        <v>Aucune grille CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutre = dans le gamut · rouge = hors gamut</v>
+        <v>Chargement…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL de profil non valide :</v>
+        <v>Neutre = dans le gamut · rouge = hors gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Impossible de récupérer le profil depuis</v>
+        <v>URL de profil non valide :</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Charger un profil ICC depuis ce site externe ?</v>
+        <v>Impossible de récupérer le profil depuis</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Chargement du rapport Profile Assessment WG…</v>
+        <v>Charger un profil ICC depuis ce site externe ?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Exécution des contrôles Profile Assessment WG…</v>
+        <v>Chargement du rapport Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Rapport Profile Assessment WG</v>
+        <v>Exécution des contrôles Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sécurité</v>
+        <v>Rapport Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformité</v>
+        <v>Sécurité</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualité</v>
+        <v>Conformité</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORT</v>
+        <v>Qualité</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Fr.xlsx
+++ b/translations/Eng-Fr.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Profil HDR dans la chaîne</v>
+        <v>Profil HDR ColorSpace dans la chaîne</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Les transformations via un profil HDR utilisent son AToB0Tag — le rendu SDR figé exigé par la clause 8.10.6 — car la clause 8.10.1 ne lui laisse aucune balise TRC. Le résultat est ce repli, pas un comportement HDR.</v>
+        <v>Les transformations via un profil HDR ColorSpace utilisent son AToB0Tag — le rendu SDR figé exigé par la clause 8.7.1.5 — car un profil ColorSpace ne comporte aucune balise TRC. Le résultat est ce repli, pas un comportement HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Ce sont des profils HDR, sans balises TRC : le gamut est donc construit à partir de l’AToB0Tag, le rendu SDR figé qu’exige la clause 8.10.6 pour les consommateurs sans traitement HDR. Ce n’est pas le gamut HDR du profil, qui ne peut être tracé dans un PCS borné.</v>
+        <v>Ce sont des profils HDR ColorSpace, sans balises TRC : le gamut est donc construit à partir de l’AToB0Tag, le rendu SDR figé qu’exige la clause 8.7.1.5 pour les consommateurs sans traitement HDR. Ce n’est pas le gamut HDR du profil, qui ne peut être tracé dans un PCS borné.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Fichier 1,0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (classement de la clause 8.10.3)</v>
+        <v>Auto (classement de la clause 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Profils HDR</v>
+        <v>Profils HDR ColorSpace</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Profils HDR — transfert linéaire</v>
+        <v>Profils HDR ColorSpace — transfert linéaire</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>Profils HDR — transfert PQ / HLG</v>
+        <v>Profils HDR ColorSpace — transfert PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} contient de la lumière linéaire : seuls les profils HDR à transfert linéaire peuvent être assignés.</v>
+        <v>{format} contient de la lumière linéaire : seuls les profils HDR ColorSpace à transfert linéaire peuvent être assignés.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} profil(s) HDR PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR › Transfert non linéaire.</v>
+        <v>{n} profil(s) HDR ColorSpace PQ/HLG du pool ne sont pas proposés — le panneau Profils les liste sous Profils HDR ColorSpace › Transfert non linéaire.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Aucun profil HDR à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR par transfert.</v>
+        <v>Aucun profil HDR ColorSpace à transfert linéaire dans le pool pour l’instant ; le panneau Profils regroupe les profils HDR ColorSpace par transfert.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.10.3).</v>
+        <v>Primaires non spécifiées : pas de chemin HDR dans cette version</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Réserve de l’écran</v>
+        <v>IccProfLib refuse d’appliquer cette courbe de gain : {why}. Un CMM passe au descripteur de tone mapping suivant (clause 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
+        <v>Réserve de l’écran</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Référence</v>
+        <v>{n} diaphragmes (≈{r}× le blanc de référence)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Aperçu via le moteur couleur</v>
+        <v>Référence</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Tel que créé (base {h} diaphs, sans gain)</v>
+        <v>Aperçu via le moteur couleur</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Mappé pour {h} diaphs</v>
+        <v>Tel que créé (base {h} diaphs, sans gain)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
+        <v>Mappé pour {h} diaphs</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>blanc de référence</v>
+        <v>Les mêmes pixels de test (signal {transfer} croissant de gauche à droite : gris, puis R, V, B, J, C, M) passés par la transformation HDR d’IccProfLib. Les deux bandes sont plafonnées à {r}× le blanc de référence HDR, comme les montrerait un écran disposant de {h} diaphs de marge : là où la bande du haut sature à plat, la courbe de gain adoucit les hautes lumières.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>pic de l’écran</v>
+        <v>blanc de référence</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Aperçu indisponible : {why}</v>
+        <v>pic de l’écran</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
+        <v>Aperçu indisponible : {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Gain pour toutes les marges</v>
+        <v>le moteur couleur n’a pas pris le chemin HDR pour ce profil</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
+        <v>Gain pour toutes les marges</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
+        <v>Gain appliqué à une entrée grise pour chaque marge d’affichage : le bleu compresse, le rouge étend, le blanc ne change rien. Les pointillés marquent les courbes du tag, le trait plein la base, la ligne ambre le curseur ; la diagonale en tirets est l’endroit où l’entrée atteint le pic de l’écran. Cliquez pour déplacer le curseur.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Marge de l’écran (diaphs)</v>
+        <v>Entrée (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Gain (diaphs)</v>
+        <v>Marge de l’écran (diaphs)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Courbe du tag</v>
+        <v>Gain (diaphs)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Base</v>
+        <v>Courbe du tag</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Curseur</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Entrée = pic de l’écran</v>
+        <v>Curseur</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Courbes de tons gris par marge</v>
+        <v>Entrée = pic de l’écran</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
+        <v>Courbes de tons gris par marge</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
+        <v>La courbe de tons gris à chaque marge stockée dans le tag, colorée du bas (bleu) au haut (rouge), avec la courbe du curseur en ambre. Les deux axes sont en diaphs : la diagonale signifie aucun changement.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} diaphs</v>
+        <v>Sortie (diaphs par rapport au blanc de référence HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} diaphs (base)</v>
+        <v>{h} diaphs</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>À {h} diaphs (curseur)</v>
+        <v>{h} diaphs (base)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
+        <v>À {h} diaphs (curseur)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
+        <v>Courbes du tag, par réserve : {list} diaphragmes. Référence {b} diaphragmes, blanc de référence HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
+        <v>Cette réserve est hors de la plage des courbes du tag ; la courbe la plus proche est utilisée telle quelle — la bibliothèque n’extrapole pas au-delà.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
+        <v>Certaines pentes sont dérivées (PCHIP) et non stockées dans le tag. Cette dérivation reconstitue une clause SMPTE ; considérez la forme de ces courbes comme provisoire.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
+        <v>Le tag demande un tone mapping sur le blanc de référence ; ses courbes sont donc construites par la bibliothèque au lieu d’être lues dans le fichier (construction issue d’un projet de comité).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
+        <v>Aucune image alternative : le tag ne demande aucun tone mapping, seulement un écrêtage au volume colorimétrique de l’écran.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Courbe à {h} diaphragmes (sans gain)</v>
+        <v>Les deux courbes mélangées à cette réserve combinent les canaux différemment ; il n’existe donc pas de courbe de gain unique à tracer. La courbe de tons ci-dessous reste exacte.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Courbe à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes (sans gain)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Appliqué à {h} diaphragmes</v>
+        <v>Courbe à {h} diaphragmes</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Gain appliqué à cette réserve</v>
+        <v>Appliqué à {h} diaphragmes</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
+        <v>Gain appliqué à cette réserve</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Gain (diaphragmes log2)</v>
+        <v>Entrée mélangée (linéaire, 1,0 = blanc de référence HDR)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Courbe de tons des gris à cette réserve</v>
+        <v>Gain (diaphragmes log2)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Entrée (× blanc de référence HDR)</v>
+        <v>Courbe de tons des gris à cette réserve</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Sortie (× blanc de référence HDR)</v>
+        <v>Entrée (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Sans changement</v>
+        <v>Sortie (× blanc de référence HDR)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Pic de l’écran à {h} diaphragmes</v>
+        <v>Sans changement</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Sortie à {h} diaphragmes</v>
+        <v>Pic de l’écran à {h} diaphragmes</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
+        <v>Sortie à {h} diaphragmes</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Identifier les écrans</v>
+        <v>HDR, gamut et rapport de pixels se mettent à jour quand la fenêtre passe sur un écran où ils diffèrent.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
+        <v>Identifier les écrans</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
+        <v>Demande l’autorisation de savoir sur quel écran se trouve cette fenêtre, pour que le panneau se mette aussi à jour entre deux écrans semblables et affiche la réserve HDR si le navigateur l’expose.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
+        <v>Suivi de l’écran sur lequel se trouve cette fenêtre.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
+        <v>L’autorisation d’identifier les écrans a été refusée. Elle peut être modifiée dans les paramètres de ce site.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>Impossible d’identifier les écrans.</v>
+        <v>Ce navigateur ne peut pas identifier les écrans ; seule la mise à jour automatique ci-dessus s’applique.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Événements d’affichage</v>
+        <v>Impossible d’identifier les écrans.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
+        <v>Événements d’affichage</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Primaires de couleur</v>
+        <v>Aucun événement pour l’instant. Faites glisser la fenêtre vers un autre écran.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Caractéristiques de transfert</v>
+        <v>Primaires de couleur</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Coefficients de matrice</v>
+        <v>Caractéristiques de transfert</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Indicateur de plage vidéo complète</v>
+        <v>Coefficients de matrice</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Plage complète</v>
+        <v>Indicateur de plage vidéo complète</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Plage réduite</v>
+        <v>Plage complète</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>non attribué par l’UIT-T H.273</v>
+        <v>Plage réduite</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
+        <v>non attribué par l’UIT-T H.273</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
+        <v>La valeur 2 (Non spécifié) des primaires renvoie au profil lui-même : les primaires proviennent des balises de colorant et non de cette balise.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>RAPPORT</v>
+        <v>Les quatre octets réservés de cette balise ne sont pas tous nuls.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>ÉCHEC</v>
+        <v>RAPPORT</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>contrôles</v>
+        <v>ÉCHEC</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
+        <v>contrôles</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>Outil de profil ICC · propulsé par IccProfLib</v>
+        <v>Généré par iccPawgReport (iccDEV) · liste de contrôle de l’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>Outil de profil ICC</v>
+        <v>Outil de profil ICC · propulsé par IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Propulsé par {lib}</v>
+        <v>Outil de profil ICC</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>S’abonner</v>
+        <v>Propulsé par {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Être notifié des nouvelles versions de profiletool</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Être notifié des nouvelles versions</v>
+        <v>Être notifié des nouvelles versions de profiletool</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Fermer</v>
+        <v>Être notifié des nouvelles versions</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>Adresse e-mail</v>
+        <v>Nous vous enverrons un e-mail à chaque sortie d’une version majeure ou mineure de profiletool. Les versions correctives sont exclues. Votre adresse est vérifiée manuellement avant d’être ajoutée.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>vous@exemple.com</v>
+        <v>Adresse e-mail</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>Comment utiliserez-vous profiletool ?</v>
+        <v>vous@exemple.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(facultatif)</v>
+        <v>Comment utiliserez-vous profiletool ?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
+        <v>(facultatif)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
+        <v>p. ex. évaluer des profils ICC pour le calage presse</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Annuler</v>
+        <v>J’accepte de recevoir des e-mails à propos des versions de profiletool. Je peux me désabonner à tout moment.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>S’abonner</v>
+        <v>Annuler</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Merci — nous reviendrons vers vous.</v>
+        <v>S’abonner</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
+        <v>Merci — nous reviendrons vers vous.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Fermer</v>
+        <v>Après validation, vous recevrez un e-mail de bienvenue. Ensuite, vous ne serez recontacté qu’à la sortie d’une nouvelle version de profiletool.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Avis de confidentialité</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Veuillez saisir une adresse e-mail valide.</v>
+        <v>Avis de confidentialité</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
+        <v>Veuillez saisir une adresse e-mail valide.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Veuillez vérifier le formulaire et réessayer.</v>
+        <v>Trop de requêtes. Veuillez réessayer plus tard.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
+        <v>Veuillez vérifier le formulaire et réessayer.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Erreur réseau. Veuillez réessayer.</v>
+        <v>Impossible d’envoyer votre demande. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Erreur :</v>
+        <v>Erreur réseau. Veuillez réessayer.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>Convertir en XML</v>
+        <v>Erreur :</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>Convertir en JSON</v>
+        <v>Convertir en XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>Convertir en ICC</v>
+        <v>Convertir en JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>Conversion en XML…</v>
+        <v>Convertir en ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>Conversion en JSON…</v>
+        <v>Conversion en XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>Conversion en ICC…</v>
+        <v>Conversion en JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>Charger un profil ICC</v>
+        <v>Conversion en ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Zone de dépôt pour les fichiers de profil ICC</v>
+        <v>Charger un profil ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>ID du profil</v>
+        <v>Zone de dépôt pour les fichiers de profil ICC</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>Aucune balise trouvée.</v>
+        <v>ID du profil</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Nom de balise</v>
+        <v>Aucune balise trouvée.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Nom de balise</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Décalage</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Taille</v>
+        <v>Décalage</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Rembourrage</v>
+        <v>Taille</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Octets modifiés depuis le chargement</v>
+        <v>Rembourrage</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Type</v>
+        <v>Octets modifiés depuis le chargement</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Tableau de {type}</v>
+        <v>Type</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Aucun contenu)</v>
+        <v>Tableau de {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>octets</v>
+        <v>(Aucun contenu)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>Chargement de la description complète…</v>
+        <v>octets</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>Impossible de charger la description complète :</v>
+        <v>Chargement de la description complète…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
+        <v>Impossible de charger la description complète :</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
+        <v>Ce profil n’a pas pu être entièrement analysé et ne doit pas être appliqué. L’en-tête et le répertoire de balises ci-dessous sont affichés à titre d’inspection uniquement.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Aucune sortie de validation</v>
+        <v>Contenu de la balise indisponible — le profil n’a pas pu être entièrement analysé.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>Le profil est valide</v>
+        <v>Aucune sortie de validation</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Le profil comporte des avertissements</v>
+        <v>Le profil est valide</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>Le profil est non conforme</v>
+        <v>Le profil comporte des avertissements</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Erreur de validation critique</v>
+        <v>Le profil est non conforme</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>État de validation inconnu</v>
+        <v>Erreur de validation critique</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Critique — affiché à titre d’inspection uniquement</v>
+        <v>État de validation inconnu</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>Aucun avertissement ni erreur trouvés.</v>
+        <v>Critique — affiché à titre d’inspection uniquement</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Valide</v>
+        <v>Aucun avertissement ni erreur trouvés.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Avertissement</v>
+        <v>Valide</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Erreur</v>
+        <v>Avertissement</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Inconnu</v>
+        <v>Erreur</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Réussi</v>
+        <v>Inconnu</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Échec</v>
+        <v>Réussi</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Voir dans le contexte</v>
+        <v>Échec</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Détail de validation</v>
+        <v>Voir dans le contexte</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Déclenché par</v>
+        <v>Détail de validation</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Champ</v>
+        <v>Déclenché par</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Valeur actuelle</v>
+        <v>Champ</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Requis : 0</v>
+        <v>Valeur actuelle</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Attendu : {value}</v>
+        <v>Requis : 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>Non valide</v>
+        <v>Attendu : {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
+        <v>Non valide</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Fermer</v>
+        <v>Ce résultat n'a pas pu être associé à un champ spécifique.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>Chargement de l’éditeur XML…</v>
+        <v>Fermer</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Chargement de l’éditeur JSON…</v>
+        <v>Chargement de l’éditeur XML…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Chargement de l’éditeur JSON…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
+        <v>Vous avez des modifications XML non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● modifications XML non enregistrées</v>
+        <v>Vous avez des modifications JSON non enregistrées. Les écraser avec une nouvelle conversion depuis le profil ICC ?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● modifications JSON non enregistrées</v>
+        <v>● modifications XML non enregistrées</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifications JSON non enregistrées</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en XML&lt;/em&gt; pour générer une représentation XML modifiable de ce profil. Le XML est produit par le même chemin de code IccLibXML utilisé par l’outil &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>indentation</v>
+        <v>Cliquez sur &lt;em&gt;Convertir en JSON&lt;/em&gt; pour générer une représentation JSON modifiable de ce profil. Le JSON est produit par le même chemin de code IccLibJSON utilisé par l’outil &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>trier les clés</v>
+        <v>indentation</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>trier les clés</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Profil écrit depuis les modifications, mais la revalidation a échoué :</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>